--- a/01_Data/01_Derived/pca_ds_total.xlsx
+++ b/01_Data/01_Derived/pca_ds_total.xlsx
@@ -712,19 +712,19 @@
         <v>-0.0881981184524136</v>
       </c>
       <c r="F2">
-        <v>2.058249087988643</v>
+        <v>3.42284431543177</v>
       </c>
       <c r="G2">
-        <v>-1.145109845431552</v>
+        <v>-1.533496411400556</v>
       </c>
       <c r="H2">
-        <v>-0.4288595452115398</v>
+        <v>-0.892421773181873</v>
       </c>
       <c r="I2">
-        <v>-0.3960634271100602</v>
+        <v>-0.9097235331120618</v>
       </c>
       <c r="J2">
-        <v>0.5136184984558807</v>
+        <v>1.507314925508106</v>
       </c>
       <c r="K2">
         <v>2.217690973400964</v>
@@ -784,19 +784,19 @@
         <v>0.4500999512679</v>
       </c>
       <c r="AD2">
-        <v>1.839010871902225</v>
+        <v>1.674909473220988</v>
       </c>
       <c r="AE2">
-        <v>-2.161913593890198</v>
+        <v>-2.380681016321146</v>
       </c>
       <c r="AF2">
-        <v>-0.04420605477791918</v>
+        <v>-0.09292194364106034</v>
       </c>
       <c r="AG2">
-        <v>-0.5333685648376264</v>
+        <v>0.3786833157667859</v>
       </c>
       <c r="AH2">
-        <v>0.2666304125916659</v>
+        <v>-0.4535418681551858</v>
       </c>
       <c r="AI2">
         <v>0.6010168790327229</v>
@@ -919,19 +919,19 @@
         <v>0.1335014893141034</v>
       </c>
       <c r="F3">
-        <v>-0.5068052052360665</v>
+        <v>-0.7717797708657451</v>
       </c>
       <c r="G3">
-        <v>1.233262103925824</v>
+        <v>1.186552916365934</v>
       </c>
       <c r="H3">
-        <v>0.6099211008706608</v>
+        <v>0.5318995677608463</v>
       </c>
       <c r="I3">
-        <v>-0.1464040629102908</v>
+        <v>-0.07896075099881338</v>
       </c>
       <c r="J3">
-        <v>-0.4953117318819929</v>
+        <v>-0.3594430567463361</v>
       </c>
       <c r="K3">
         <v>-1.852320403982484</v>
@@ -991,19 +991,19 @@
         <v>0.3521665641876552</v>
       </c>
       <c r="AD3">
-        <v>1.639520822575078</v>
+        <v>2.373527678234779</v>
       </c>
       <c r="AE3">
-        <v>1.68066208560771</v>
+        <v>1.533615558327731</v>
       </c>
       <c r="AF3">
-        <v>-0.3954520239065</v>
+        <v>-0.5320391578089255</v>
       </c>
       <c r="AG3">
-        <v>0.1580503838153209</v>
+        <v>0.4743350767728872</v>
       </c>
       <c r="AH3">
-        <v>-0.08479564373818936</v>
+        <v>0.2865769627058879</v>
       </c>
       <c r="AI3">
         <v>-0.703779301220137</v>
@@ -1126,19 +1126,19 @@
         <v>0.2045763110614248</v>
       </c>
       <c r="F4">
-        <v>0.4253190302663208</v>
+        <v>-0.1403541775755958</v>
       </c>
       <c r="G4">
-        <v>3.00744586847724</v>
+        <v>3.098240538559619</v>
       </c>
       <c r="H4">
-        <v>1.403944349525694</v>
+        <v>1.21722355064949</v>
       </c>
       <c r="I4">
-        <v>-0.3349251825504388</v>
+        <v>-0.4282510181520727</v>
       </c>
       <c r="J4">
-        <v>0.09842897848026916</v>
+        <v>0.2124974449650371</v>
       </c>
       <c r="K4">
         <v>2.588933119157866</v>
@@ -1198,19 +1198,19 @@
         <v>0.2066757114866901</v>
       </c>
       <c r="AD4">
-        <v>0.5535312598093336</v>
+        <v>1.309094707903618</v>
       </c>
       <c r="AE4">
-        <v>0.9887228562416728</v>
+        <v>1.012878724013655</v>
       </c>
       <c r="AF4">
-        <v>1.100558360246861</v>
+        <v>1.106748918874793</v>
       </c>
       <c r="AG4">
-        <v>-0.1432162381070479</v>
+        <v>-0.2160728175462882</v>
       </c>
       <c r="AH4">
-        <v>-0.05552146679948636</v>
+        <v>-0.2268437120685775</v>
       </c>
       <c r="AI4">
         <v>-2.293825235352618</v>
@@ -1333,19 +1333,19 @@
         <v>0.1356996796774226</v>
       </c>
       <c r="F5">
-        <v>0.585382632169328</v>
+        <v>0.228400519118905</v>
       </c>
       <c r="G5">
-        <v>1.779718760704279</v>
+        <v>1.874593011276473</v>
       </c>
       <c r="H5">
-        <v>-0.8116316221226437</v>
+        <v>-0.8185357761798473</v>
       </c>
       <c r="I5">
-        <v>-1.056767516931022</v>
+        <v>-0.79052969731117</v>
       </c>
       <c r="J5">
-        <v>-0.8655267720879434</v>
+        <v>-1.15546881470155</v>
       </c>
       <c r="K5">
         <v>-0.3449889226073376</v>
@@ -1405,19 +1405,19 @@
         <v>-0.2654297656509095</v>
       </c>
       <c r="AD5">
-        <v>0.286072138613866</v>
+        <v>0.6467950960163521</v>
       </c>
       <c r="AE5">
-        <v>0.4347621279891651</v>
+        <v>0.5161127085251456</v>
       </c>
       <c r="AF5">
-        <v>1.561363062943767</v>
+        <v>1.485493810930482</v>
       </c>
       <c r="AG5">
-        <v>-0.2261745448323392</v>
+        <v>0.8981211785080475</v>
       </c>
       <c r="AH5">
-        <v>0.06577518121067361</v>
+        <v>-0.02632956961950246</v>
       </c>
       <c r="AI5">
         <v>-2.417442455825573</v>
@@ -1540,19 +1540,19 @@
         <v>-2.425425185199579</v>
       </c>
       <c r="F6">
-        <v>0.8414813909967314</v>
+        <v>0.6806476334092064</v>
       </c>
       <c r="G6">
-        <v>-0.2902292231515735</v>
+        <v>-0.0009781325340130296</v>
       </c>
       <c r="H6">
-        <v>0.9075160685869437</v>
+        <v>1.068873274982947</v>
       </c>
       <c r="I6">
-        <v>0.7996414897689496</v>
+        <v>1.043723594594904</v>
       </c>
       <c r="J6">
-        <v>-0.9893101061251013</v>
+        <v>-0.8322833185649728</v>
       </c>
       <c r="K6">
         <v>1.405629844539485</v>
@@ -1612,19 +1612,19 @@
         <v>-0.4259815981336719</v>
       </c>
       <c r="AD6">
-        <v>1.400753956318101</v>
+        <v>1.557404047764492</v>
       </c>
       <c r="AE6">
-        <v>-0.8975277534409311</v>
+        <v>-1.081104288325204</v>
       </c>
       <c r="AF6">
-        <v>-0.9227941135775906</v>
+        <v>-0.8707781658455418</v>
       </c>
       <c r="AG6">
-        <v>0.552029611871715</v>
+        <v>-0.7670585645275999</v>
       </c>
       <c r="AH6">
-        <v>-0.064916977753503</v>
+        <v>0.3907154835304485</v>
       </c>
       <c r="AI6">
         <v>1.521428072365983</v>
@@ -1747,19 +1747,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F7">
-        <v>-0.3617624276915842</v>
+        <v>-0.6363313031490199</v>
       </c>
       <c r="G7">
-        <v>1.620643623449947</v>
+        <v>1.547538651270073</v>
       </c>
       <c r="H7">
-        <v>0.6071197162182528</v>
+        <v>0.4443717452497976</v>
       </c>
       <c r="I7">
-        <v>0.1216380661047786</v>
+        <v>-0.1344472182589013</v>
       </c>
       <c r="J7">
-        <v>0.7743877549468825</v>
+        <v>0.9468755366596031</v>
       </c>
       <c r="K7">
         <v>0.3599740314329107</v>
@@ -1819,19 +1819,19 @@
         <v>-0.01553336719039279</v>
       </c>
       <c r="AD7">
-        <v>-1.030632857018809</v>
+        <v>-1.129565510229344</v>
       </c>
       <c r="AE7">
-        <v>0.7832096851529837</v>
+        <v>0.8872369918669004</v>
       </c>
       <c r="AF7">
-        <v>-0.112785492770087</v>
+        <v>-0.09777549414992587</v>
       </c>
       <c r="AG7">
-        <v>-0.1922963360953172</v>
+        <v>-0.2059988563222577</v>
       </c>
       <c r="AH7">
-        <v>-0.1321071363263636</v>
+        <v>-0.242572595697764</v>
       </c>
       <c r="AI7">
         <v>-0.3577792633748267</v>
@@ -1954,19 +1954,19 @@
         <v>-0.09301633008136695</v>
       </c>
       <c r="F8">
-        <v>0.8624132329466511</v>
+        <v>0.921045171193385</v>
       </c>
       <c r="G8">
-        <v>-0.465799874067906</v>
+        <v>-0.3022212679529683</v>
       </c>
       <c r="H8">
-        <v>0.6327464860405835</v>
+        <v>0.6779612387917573</v>
       </c>
       <c r="I8">
-        <v>0.164733102738788</v>
+        <v>0.1044593593218454</v>
       </c>
       <c r="J8">
-        <v>0.2247995565871126</v>
+        <v>0.2581916420824911</v>
       </c>
       <c r="K8">
         <v>1.517561766944163</v>
@@ -2026,19 +2026,19 @@
         <v>-1.095490471750341</v>
       </c>
       <c r="AD8">
-        <v>0.484234626465866</v>
+        <v>0.816670002348032</v>
       </c>
       <c r="AE8">
-        <v>0.9016786126393537</v>
+        <v>0.8579652210802351</v>
       </c>
       <c r="AF8">
-        <v>0.06281784227073628</v>
+        <v>-0.0004835766667685704</v>
       </c>
       <c r="AG8">
-        <v>-0.275421491205485</v>
+        <v>0.160558286733528</v>
       </c>
       <c r="AH8">
-        <v>0.04290856788822662</v>
+        <v>-0.2491823506751376</v>
       </c>
       <c r="AI8">
         <v>1.182224938379928</v>
@@ -2161,19 +2161,19 @@
         <v>-0.8233556639411008</v>
       </c>
       <c r="F9">
-        <v>0.7789745909031167</v>
+        <v>0.6309371552400868</v>
       </c>
       <c r="G9">
-        <v>0.188917271179123</v>
+        <v>0.3622346986060679</v>
       </c>
       <c r="H9">
-        <v>-1.471454806526667</v>
+        <v>-1.303881359734717</v>
       </c>
       <c r="I9">
-        <v>-0.02652557400423824</v>
+        <v>0.3472755466398721</v>
       </c>
       <c r="J9">
-        <v>-1.037015789269914</v>
+        <v>-1.33105687573681</v>
       </c>
       <c r="K9">
         <v>1.998167464452126</v>
@@ -2233,19 +2233,19 @@
         <v>-0.9199175350395553</v>
       </c>
       <c r="AD9">
-        <v>0.9544907682887368</v>
+        <v>1.480547118617274</v>
       </c>
       <c r="AE9">
-        <v>-0.7053052633378093</v>
+        <v>-0.7047508648155589</v>
       </c>
       <c r="AF9">
-        <v>0.7752419964191987</v>
+        <v>0.8862043579006624</v>
       </c>
       <c r="AG9">
-        <v>1.284857085131493</v>
+        <v>-0.5030136555986374</v>
       </c>
       <c r="AH9">
-        <v>0.08938053465369108</v>
+        <v>1.192419903014491</v>
       </c>
       <c r="AI9">
         <v>1.912043829547578</v>
@@ -2368,19 +2368,19 @@
         <v>-0.6239972066354981</v>
       </c>
       <c r="F10">
-        <v>-1.294546914989528</v>
+        <v>-1.671083209979987</v>
       </c>
       <c r="G10">
-        <v>2.483826555023258</v>
+        <v>2.227547670481409</v>
       </c>
       <c r="H10">
-        <v>0.07146957871475745</v>
+        <v>-0.1462104219181613</v>
       </c>
       <c r="I10">
-        <v>-0.8976782121991224</v>
+        <v>-0.7951770301505205</v>
       </c>
       <c r="J10">
-        <v>-0.8020781549380969</v>
+        <v>-0.6661761197874133</v>
       </c>
       <c r="K10">
         <v>-2.602793855070577</v>
@@ -2440,19 +2440,19 @@
         <v>-0.1974076961736443</v>
       </c>
       <c r="AD10">
-        <v>-0.7517887276083034</v>
+        <v>-0.6274153035400012</v>
       </c>
       <c r="AE10">
-        <v>0.919503235497841</v>
+        <v>1.04279467997204</v>
       </c>
       <c r="AF10">
-        <v>0.08970174053489077</v>
+        <v>0.1081640545591804</v>
       </c>
       <c r="AG10">
-        <v>-0.1429814449533513</v>
+        <v>0.5328055889351268</v>
       </c>
       <c r="AH10">
-        <v>0.0544915088779469</v>
+        <v>-0.01234144655085356</v>
       </c>
       <c r="AI10">
         <v>-1.278817028988705</v>
@@ -2575,19 +2575,19 @@
         <v>-0.09856838280264232</v>
       </c>
       <c r="F11">
-        <v>-2.74233717358236</v>
+        <v>-2.933906360080433</v>
       </c>
       <c r="G11">
-        <v>1.863985693281235</v>
+        <v>1.338524895872511</v>
       </c>
       <c r="H11">
-        <v>1.240164242497325</v>
+        <v>0.835342904325045</v>
       </c>
       <c r="I11">
-        <v>-2.020892827299455</v>
+        <v>-2.648666702213545</v>
       </c>
       <c r="J11">
-        <v>2.373844224158865</v>
+        <v>2.076913909699694</v>
       </c>
       <c r="K11">
         <v>-0.4255898130840945</v>
@@ -2647,19 +2647,19 @@
         <v>-0.03017150882241717</v>
       </c>
       <c r="AD11">
-        <v>-2.816074698359538</v>
+        <v>-3.325408717264688</v>
       </c>
       <c r="AE11">
-        <v>-0.003090880287206499</v>
+        <v>0.3316679116404281</v>
       </c>
       <c r="AF11">
-        <v>0.6670562567888787</v>
+        <v>0.8178752092893854</v>
       </c>
       <c r="AG11">
-        <v>-0.09880773744064668</v>
+        <v>-0.2991914989672441</v>
       </c>
       <c r="AH11">
-        <v>-0.09434933505130029</v>
+        <v>-0.1754227831429641</v>
       </c>
       <c r="AI11">
         <v>1.667641081790977</v>
@@ -2782,19 +2782,19 @@
         <v>-0.2046198197230022</v>
       </c>
       <c r="F12">
-        <v>0.1842835290951261</v>
+        <v>0.7334067726389021</v>
       </c>
       <c r="G12">
-        <v>-0.5269721099026301</v>
+        <v>-0.7681558693526773</v>
       </c>
       <c r="H12">
-        <v>-0.2346104841867937</v>
+        <v>-0.4002220337092263</v>
       </c>
       <c r="I12">
-        <v>0.833651325108142</v>
+        <v>0.7933916774438361</v>
       </c>
       <c r="J12">
-        <v>-0.6352297699373944</v>
+        <v>0.05872973812425888</v>
       </c>
       <c r="K12">
         <v>-0.6564236495197475</v>
@@ -2854,19 +2854,19 @@
         <v>-0.1656388492017512</v>
       </c>
       <c r="AD12">
-        <v>0.4420481621236587</v>
+        <v>0.399808518196247</v>
       </c>
       <c r="AE12">
-        <v>-0.05278668746363599</v>
+        <v>-0.1365285313856276</v>
       </c>
       <c r="AF12">
-        <v>-0.3085787095013065</v>
+        <v>-0.3566454126513431</v>
       </c>
       <c r="AG12">
-        <v>0.03893663602594179</v>
+        <v>0.02513466551003203</v>
       </c>
       <c r="AH12">
-        <v>0.176177211278078</v>
+        <v>0.04770616423561684</v>
       </c>
       <c r="AI12">
         <v>1.222722466304828</v>
@@ -2989,19 +2989,19 @@
         <v>-0.2503058035649426</v>
       </c>
       <c r="F13">
-        <v>-1.265555569106477</v>
+        <v>-1.467201579127649</v>
       </c>
       <c r="G13">
-        <v>1.130788815213389</v>
+        <v>0.9282995970976597</v>
       </c>
       <c r="H13">
-        <v>-0.00332470122766689</v>
+        <v>-0.1038915557609943</v>
       </c>
       <c r="I13">
-        <v>-0.6475321466941368</v>
+        <v>-0.5601650417379405</v>
       </c>
       <c r="J13">
-        <v>-0.3585707796121328</v>
+        <v>-0.4611116163163456</v>
       </c>
       <c r="K13">
         <v>2.086641144892489</v>
@@ -3061,19 +3061,19 @@
         <v>-0.4335859120886792</v>
       </c>
       <c r="AD13">
-        <v>-0.719728652995319</v>
+        <v>-0.3696884398673731</v>
       </c>
       <c r="AE13">
-        <v>1.010463836395759</v>
+        <v>1.206280804578066</v>
       </c>
       <c r="AF13">
-        <v>0.2979674603133923</v>
+        <v>0.3612684430453962</v>
       </c>
       <c r="AG13">
-        <v>0.01996820216189975</v>
+        <v>1.09631856527921</v>
       </c>
       <c r="AH13">
-        <v>0.127287515991992</v>
+        <v>0.3020710526710936</v>
       </c>
       <c r="AI13">
         <v>-2.401432627929076</v>
@@ -3196,19 +3196,19 @@
         <v>-0.1023930276848194</v>
       </c>
       <c r="F14">
-        <v>0.2844862543937555</v>
+        <v>1.150868438032686</v>
       </c>
       <c r="G14">
-        <v>-1.190695441170871</v>
+        <v>-1.548742456340913</v>
       </c>
       <c r="H14">
-        <v>-0.940826012531005</v>
+        <v>-1.151069840634091</v>
       </c>
       <c r="I14">
-        <v>0.9336525919571101</v>
+        <v>0.8919892468831386</v>
       </c>
       <c r="J14">
-        <v>-1.026575510571312</v>
+        <v>-0.01800782502219997</v>
       </c>
       <c r="K14">
         <v>-2.248368434954414</v>
@@ -3268,19 +3268,19 @@
         <v>0.5709456679467313</v>
       </c>
       <c r="AD14">
-        <v>-2.448164083597422</v>
+        <v>-3.87935852261573</v>
       </c>
       <c r="AE14">
-        <v>-2.533752332922437</v>
+        <v>-2.361396603996886</v>
       </c>
       <c r="AF14">
-        <v>-0.5505917781927652</v>
+        <v>-0.3857681562000246</v>
       </c>
       <c r="AG14">
-        <v>0.5018541235200097</v>
+        <v>-0.3161152352356665</v>
       </c>
       <c r="AH14">
-        <v>0.03771862557027159</v>
+        <v>0.4547626045665553</v>
       </c>
       <c r="AI14">
         <v>1.24396909459483</v>
@@ -3403,19 +3403,19 @@
         <v>0.136432409798529</v>
       </c>
       <c r="F15">
-        <v>-1.614332701556931</v>
+        <v>-1.477293662123702</v>
       </c>
       <c r="G15">
-        <v>-0.9621181694679224</v>
+        <v>-1.210170955714605</v>
       </c>
       <c r="H15">
-        <v>-1.529450066586521</v>
+        <v>-1.443183749809393</v>
       </c>
       <c r="I15">
-        <v>0.1958955179460102</v>
+        <v>0.466039533068963</v>
       </c>
       <c r="J15">
-        <v>-0.87904572592466</v>
+        <v>-0.9620933173008346</v>
       </c>
       <c r="K15">
         <v>-10.6709885080744</v>
@@ -3475,19 +3475,19 @@
         <v>0.3268136553331363</v>
       </c>
       <c r="AD15">
-        <v>-2.366223663349591</v>
+        <v>-2.626024366575254</v>
       </c>
       <c r="AE15">
-        <v>1.010965399440677</v>
+        <v>1.285150555238636</v>
       </c>
       <c r="AF15">
-        <v>0.6720882630417219</v>
+        <v>0.7249899549238439</v>
       </c>
       <c r="AG15">
-        <v>-0.002134191495940114</v>
+        <v>0.07017892001911823</v>
       </c>
       <c r="AH15">
-        <v>0.1566707702014022</v>
+        <v>0.006548175710276948</v>
       </c>
       <c r="AI15">
         <v>3.234831999138365</v>
@@ -3610,19 +3610,19 @@
         <v>-0.08290690235680803</v>
       </c>
       <c r="F16">
-        <v>-0.386356039602025</v>
+        <v>-0.6550440709323352</v>
       </c>
       <c r="G16">
-        <v>1.218348315876945</v>
+        <v>1.196481552747584</v>
       </c>
       <c r="H16">
-        <v>0.8798151094800321</v>
+        <v>0.7895302756587472</v>
       </c>
       <c r="I16">
-        <v>-0.5192689687688168</v>
+        <v>-0.5254936144719552</v>
       </c>
       <c r="J16">
-        <v>-0.160688792480052</v>
+        <v>-0.1188981468837818</v>
       </c>
       <c r="K16">
         <v>-4.292817286641699</v>
@@ -3682,19 +3682,19 @@
         <v>0.8577448943219087</v>
       </c>
       <c r="AD16">
-        <v>-0.6969970275921862</v>
+        <v>-0.5523605215818573</v>
       </c>
       <c r="AE16">
-        <v>1.59507228028979</v>
+        <v>1.704520925366335</v>
       </c>
       <c r="AF16">
-        <v>0.6136790248976071</v>
+        <v>0.5121581809317804</v>
       </c>
       <c r="AG16">
-        <v>-0.1639232451893539</v>
+        <v>0.7540061107223356</v>
       </c>
       <c r="AH16">
-        <v>0.3540739444861541</v>
+        <v>0.01337425324879749</v>
       </c>
       <c r="AI16">
         <v>-2.52994147450515</v>
@@ -3817,19 +3817,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F17">
-        <v>2.088471510816313</v>
+        <v>1.688443650389325</v>
       </c>
       <c r="G17">
-        <v>0.2436358508995303</v>
+        <v>0.8665724377768403</v>
       </c>
       <c r="H17">
-        <v>3.521512584613645</v>
+        <v>3.699474928478613</v>
       </c>
       <c r="I17">
-        <v>2.479969991418783</v>
+        <v>2.496879547419395</v>
       </c>
       <c r="J17">
-        <v>-0.1303712913791851</v>
+        <v>0.2814046702248297</v>
       </c>
       <c r="K17">
         <v>3.292939021768932</v>
@@ -3889,19 +3889,19 @@
         <v>0.2491465397734204</v>
       </c>
       <c r="AD17">
-        <v>2.706526626168289</v>
+        <v>4.279948624093747</v>
       </c>
       <c r="AE17">
-        <v>1.744933841865554</v>
+        <v>1.574464490560833</v>
       </c>
       <c r="AF17">
-        <v>0.763303051694423</v>
+        <v>0.7113685980151739</v>
       </c>
       <c r="AG17">
-        <v>0.09234662178437168</v>
+        <v>-0.419649284047278</v>
       </c>
       <c r="AH17">
-        <v>-0.2599232603414567</v>
+        <v>-0.03041404937502193</v>
       </c>
       <c r="AI17">
         <v>-1.302251393701334</v>
@@ -4024,19 +4024,19 @@
         <v>-0.5416406793169418</v>
       </c>
       <c r="F18">
-        <v>0.530699304095071</v>
+        <v>0.3959144351401517</v>
       </c>
       <c r="G18">
-        <v>-0.2196798828375017</v>
+        <v>-0.01013979710712774</v>
       </c>
       <c r="H18">
-        <v>0.8026221783193906</v>
+        <v>0.9128843136825899</v>
       </c>
       <c r="I18">
-        <v>-0.3726227021013605</v>
+        <v>-0.2067038284329309</v>
       </c>
       <c r="J18">
-        <v>-0.5058920371418982</v>
+        <v>-0.6670176525940632</v>
       </c>
       <c r="K18">
         <v>2.41031457492235</v>
@@ -4096,19 +4096,19 @@
         <v>0.06865398418409721</v>
       </c>
       <c r="AD18">
-        <v>1.954505650224813</v>
+        <v>2.205755806147468</v>
       </c>
       <c r="AE18">
-        <v>-2.39594086984849</v>
+        <v>-2.557100273414268</v>
       </c>
       <c r="AF18">
-        <v>0.003155065469334251</v>
+        <v>0.1334194114620162</v>
       </c>
       <c r="AG18">
-        <v>0.4359983710422551</v>
+        <v>-0.5544516787932822</v>
       </c>
       <c r="AH18">
-        <v>-0.1681152832662953</v>
+        <v>0.3145630132961715</v>
       </c>
       <c r="AI18">
         <v>1.500887042433257</v>
@@ -4231,19 +4231,19 @@
         <v>-0.1720011481973221</v>
       </c>
       <c r="F19">
-        <v>-0.2001214749253008</v>
+        <v>-0.3632737243547166</v>
       </c>
       <c r="G19">
-        <v>0.6526351195727895</v>
+        <v>0.6308857851176762</v>
       </c>
       <c r="H19">
-        <v>-1.174503492586416</v>
+        <v>-1.126660546142085</v>
       </c>
       <c r="I19">
-        <v>-0.1495943016478149</v>
+        <v>0.1302592930882712</v>
       </c>
       <c r="J19">
-        <v>-0.9457259992549956</v>
+        <v>-1.066479966238278</v>
       </c>
       <c r="K19">
         <v>1.242949250400653</v>
@@ -4303,19 +4303,19 @@
         <v>-0.6521628633828617</v>
       </c>
       <c r="AD19">
-        <v>-1.133840325196261</v>
+        <v>-1.410123629617422</v>
       </c>
       <c r="AE19">
-        <v>-0.6454444876716638</v>
+        <v>-0.484144679482815</v>
       </c>
       <c r="AF19">
-        <v>0.310926892526216</v>
+        <v>0.4244848587111271</v>
       </c>
       <c r="AG19">
-        <v>0.546326799503141</v>
+        <v>0.0585885590983492</v>
       </c>
       <c r="AH19">
-        <v>-0.03182374948772878</v>
+        <v>0.5802215997161331</v>
       </c>
       <c r="AI19">
         <v>2.595441843504651</v>
@@ -4438,19 +4438,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F20">
-        <v>2.074228879294891</v>
+        <v>2.236476488084529</v>
       </c>
       <c r="G20">
-        <v>-1.139778415254322</v>
+        <v>-0.7720041197805912</v>
       </c>
       <c r="H20">
-        <v>0.6191188357119722</v>
+        <v>0.7567414631357448</v>
       </c>
       <c r="I20">
-        <v>0.0409682508168513</v>
+        <v>-0.03480861744990223</v>
       </c>
       <c r="J20">
-        <v>0.5400913572107005</v>
+        <v>0.3734256300698625</v>
       </c>
       <c r="K20">
         <v>1.40317292488001</v>
@@ -4510,19 +4510,19 @@
         <v>0.06086766321081837</v>
       </c>
       <c r="AD20">
-        <v>0.2439541386827118</v>
+        <v>-0.7132287867575099</v>
       </c>
       <c r="AE20">
-        <v>-2.411298196936192</v>
+        <v>-2.510256135673643</v>
       </c>
       <c r="AF20">
-        <v>0.2862584582525418</v>
+        <v>0.176233891769239</v>
       </c>
       <c r="AG20">
-        <v>-0.1853886562556104</v>
+        <v>0.7799630333050066</v>
       </c>
       <c r="AH20">
-        <v>0.235600522771273</v>
+        <v>-0.0001445140753283548</v>
       </c>
       <c r="AI20">
         <v>0.5341861394730161</v>
@@ -4645,19 +4645,19 @@
         <v>-0.2398916684573013</v>
       </c>
       <c r="F21">
-        <v>-0.1448754713018373</v>
+        <v>-0.6338620618577354</v>
       </c>
       <c r="G21">
-        <v>2.800282792255279</v>
+        <v>2.769477823883316</v>
       </c>
       <c r="H21">
-        <v>0.9663164572967696</v>
+        <v>0.7619061170130843</v>
       </c>
       <c r="I21">
-        <v>0.5116412062982862</v>
+        <v>0.4463051980376282</v>
       </c>
       <c r="J21">
-        <v>-0.421657507799614</v>
+        <v>0.1386251405832827</v>
       </c>
       <c r="K21">
         <v>-0.1289661428978731</v>
@@ -4717,19 +4717,19 @@
         <v>-1.066589013163539</v>
       </c>
       <c r="AD21">
-        <v>-0.6588373570057986</v>
+        <v>-0.3176333366947382</v>
       </c>
       <c r="AE21">
-        <v>1.147794827886895</v>
+        <v>1.303760841787839</v>
       </c>
       <c r="AF21">
-        <v>0.8148888905798231</v>
+        <v>0.8293524790013551</v>
       </c>
       <c r="AG21">
-        <v>-0.02763609644586704</v>
+        <v>0.3133460213925099</v>
       </c>
       <c r="AH21">
-        <v>-0.1971196585703887</v>
+        <v>0.04089832508423324</v>
       </c>
       <c r="AI21">
         <v>0.5273304922996142</v>
@@ -4852,19 +4852,19 @@
         <v>-0.156767315969441</v>
       </c>
       <c r="F22">
-        <v>-1.626182200666803</v>
+        <v>-1.79903120182813</v>
       </c>
       <c r="G22">
-        <v>0.9428886337010174</v>
+        <v>0.6995399503917505</v>
       </c>
       <c r="H22">
-        <v>0.852550568352754</v>
+        <v>0.7044747582820139</v>
       </c>
       <c r="I22">
-        <v>-0.4231102475630861</v>
+        <v>-0.5293084581046288</v>
       </c>
       <c r="J22">
-        <v>0.3062939313102174</v>
+        <v>0.2972716220502873</v>
       </c>
       <c r="K22">
         <v>0.2686906830110402</v>
@@ -4924,19 +4924,19 @@
         <v>-0.4982429264163822</v>
       </c>
       <c r="AD22">
-        <v>-1.169372560492755</v>
+        <v>-1.292102304250449</v>
       </c>
       <c r="AE22">
-        <v>1.38132683058839</v>
+        <v>1.466461329064531</v>
       </c>
       <c r="AF22">
-        <v>-0.4684225128038061</v>
+        <v>-0.4939394414908497</v>
       </c>
       <c r="AG22">
-        <v>0.01031079804598827</v>
+        <v>0.004626741363144924</v>
       </c>
       <c r="AH22">
-        <v>0.04876306405823146</v>
+        <v>0.01648023707964802</v>
       </c>
       <c r="AI22">
         <v>-0.9869250234509327</v>
@@ -5059,19 +5059,19 @@
         <v>0.1129412338819084</v>
       </c>
       <c r="F23">
-        <v>0.6195729646459136</v>
+        <v>0.7469756573710686</v>
       </c>
       <c r="G23">
-        <v>-2.425587590503658</v>
+        <v>-2.082034065356057</v>
       </c>
       <c r="H23">
-        <v>2.035125509596694</v>
+        <v>2.306778153766147</v>
       </c>
       <c r="I23">
-        <v>-0.5870634993621958</v>
+        <v>-0.3496916076760169</v>
       </c>
       <c r="J23">
-        <v>-0.6251378811181951</v>
+        <v>-0.9365203773843197</v>
       </c>
       <c r="K23">
         <v>2.39817243748328</v>
@@ -5131,19 +5131,19 @@
         <v>-1.240065360076277</v>
       </c>
       <c r="AD23">
-        <v>0.7788184953763202</v>
+        <v>0.992292636447352</v>
       </c>
       <c r="AE23">
-        <v>1.49403115813216</v>
+        <v>1.373781885943135</v>
       </c>
       <c r="AF23">
-        <v>-0.1959648403351637</v>
+        <v>-0.3951986693070927</v>
       </c>
       <c r="AG23">
-        <v>0.1264580002599428</v>
+        <v>0.5135809903648109</v>
       </c>
       <c r="AH23">
-        <v>0.1478332025217961</v>
+        <v>0.2551080804992961</v>
       </c>
       <c r="AI23">
         <v>-0.6728220680073502</v>
@@ -5266,19 +5266,19 @@
         <v>0.1540179327050828</v>
       </c>
       <c r="F24">
-        <v>-2.25320531510804</v>
+        <v>-2.400029107693251</v>
       </c>
       <c r="G24">
-        <v>1.964817633971202</v>
+        <v>1.441960682445332</v>
       </c>
       <c r="H24">
-        <v>0.1024598502103197</v>
+        <v>-0.3348730930956359</v>
       </c>
       <c r="I24">
-        <v>-1.753798077879982</v>
+        <v>-2.813860285399946</v>
       </c>
       <c r="J24">
-        <v>4.565813317935849</v>
+        <v>3.952393550702598</v>
       </c>
       <c r="K24">
         <v>-3.27611518562337</v>
@@ -5338,19 +5338,19 @@
         <v>0.9458288766024169</v>
       </c>
       <c r="AD24">
-        <v>-2.438255771770216</v>
+        <v>-2.976383657445853</v>
       </c>
       <c r="AE24">
-        <v>0.306178298367945</v>
+        <v>0.531582283078011</v>
       </c>
       <c r="AF24">
-        <v>0.1136118840582188</v>
+        <v>0.2029133332508586</v>
       </c>
       <c r="AG24">
-        <v>-0.519060016375249</v>
+        <v>-0.4681671976816104</v>
       </c>
       <c r="AH24">
-        <v>-0.2088968733499101</v>
+        <v>-0.6543194033587862</v>
       </c>
       <c r="AI24">
         <v>-0.1061288976218552</v>
@@ -5473,19 +5473,19 @@
         <v>0.1415615206462738</v>
       </c>
       <c r="F25">
-        <v>-0.7831651658024216</v>
+        <v>-0.7376858113665269</v>
       </c>
       <c r="G25">
-        <v>-1.067806114824731</v>
+        <v>-1.069278456454431</v>
       </c>
       <c r="H25">
-        <v>1.703471816879339</v>
+        <v>1.728365729251886</v>
       </c>
       <c r="I25">
-        <v>-1.503175106791936</v>
+        <v>-1.585329268504456</v>
       </c>
       <c r="J25">
-        <v>0.5557158155562067</v>
+        <v>0.1341731914063247</v>
       </c>
       <c r="K25">
         <v>4.113876156197155</v>
@@ -5545,19 +5545,19 @@
         <v>-0.737089923915938</v>
       </c>
       <c r="AD25">
-        <v>-1.19741415019076</v>
+        <v>-1.245203867450168</v>
       </c>
       <c r="AE25">
-        <v>-0.7007634316737044</v>
+        <v>-0.5116832734335708</v>
       </c>
       <c r="AF25">
-        <v>1.297204999663305</v>
+        <v>1.443533832686089</v>
       </c>
       <c r="AG25">
-        <v>-0.3727891096533578</v>
+        <v>-0.6122835466372533</v>
       </c>
       <c r="AH25">
-        <v>-0.1568145315603992</v>
+        <v>-0.5574531099422423</v>
       </c>
       <c r="AI25">
         <v>-0.3290731029502795</v>
@@ -5680,19 +5680,19 @@
         <v>0.5473466094551815</v>
       </c>
       <c r="F26">
-        <v>-1.769609914411626</v>
+        <v>-1.679288149192221</v>
       </c>
       <c r="G26">
-        <v>-0.7239542878979516</v>
+        <v>-0.9754753305788882</v>
       </c>
       <c r="H26">
-        <v>-0.03931769878749445</v>
+        <v>-0.04994430772956469</v>
       </c>
       <c r="I26">
-        <v>0.3194689641440414</v>
+        <v>0.3341956470581484</v>
       </c>
       <c r="J26">
-        <v>-0.2075722292496757</v>
+        <v>-0.04483015747233243</v>
       </c>
       <c r="K26">
         <v>-5.528922214609147</v>
@@ -5752,19 +5752,19 @@
         <v>1.141157254675458</v>
       </c>
       <c r="AD26">
-        <v>-2.816170168439347</v>
+        <v>-3.585170019338998</v>
       </c>
       <c r="AE26">
-        <v>0.3746014752060685</v>
+        <v>0.6168664114724995</v>
       </c>
       <c r="AF26">
-        <v>-0.3819431974105689</v>
+        <v>-0.3023821536250295</v>
       </c>
       <c r="AG26">
-        <v>-0.3318985726891804</v>
+        <v>-0.1916371023567284</v>
       </c>
       <c r="AH26">
-        <v>-0.1918424547118242</v>
+        <v>-0.3817532028923203</v>
       </c>
       <c r="AI26">
         <v>1.962647432611476</v>
@@ -5887,19 +5887,19 @@
         <v>0.4279148181511943</v>
       </c>
       <c r="F27">
-        <v>-0.1431543103635687</v>
+        <v>-0.4227285725857871</v>
       </c>
       <c r="G27">
-        <v>1.82980281261597</v>
+        <v>1.730062562110114</v>
       </c>
       <c r="H27">
-        <v>-2.155133106688512</v>
+        <v>-2.202013659999908</v>
       </c>
       <c r="I27">
-        <v>-1.675919296349388</v>
+        <v>-1.462564384986774</v>
       </c>
       <c r="J27">
-        <v>-0.3258738924277445</v>
+        <v>-0.9526210055731714</v>
       </c>
       <c r="K27">
         <v>1.924731563368451</v>
@@ -5959,19 +5959,19 @@
         <v>0.03314119926094131</v>
       </c>
       <c r="AD27">
-        <v>-1.604763454252469</v>
+        <v>-1.616853066508639</v>
       </c>
       <c r="AE27">
-        <v>1.150299316984166</v>
+        <v>1.353067812919553</v>
       </c>
       <c r="AF27">
-        <v>0.3738719193950855</v>
+        <v>0.4136795280488877</v>
       </c>
       <c r="AG27">
-        <v>0.02958769733209626</v>
+        <v>0.2340809771969301</v>
       </c>
       <c r="AH27">
-        <v>0.2668338496829629</v>
+        <v>0.08485142983033275</v>
       </c>
       <c r="AI27">
         <v>-2.489425001328669</v>
@@ -6094,19 +6094,19 @@
         <v>-0.1104174186720138</v>
       </c>
       <c r="F28">
-        <v>1.928618899158616</v>
+        <v>2.819488174710003</v>
       </c>
       <c r="G28">
-        <v>-2.07960429785743</v>
+        <v>-2.078278690689132</v>
       </c>
       <c r="H28">
-        <v>0.8502072921281248</v>
+        <v>0.690273282861622</v>
       </c>
       <c r="I28">
-        <v>-1.578527430082852</v>
+        <v>-2.026287333540451</v>
       </c>
       <c r="J28">
-        <v>1.274765982598945</v>
+        <v>1.357661069033521</v>
       </c>
       <c r="K28">
         <v>4.259220759653902</v>
@@ -6166,19 +6166,19 @@
         <v>-0.1177046804501156</v>
       </c>
       <c r="AD28">
-        <v>2.280936711820211</v>
+        <v>1.882982589982229</v>
       </c>
       <c r="AE28">
-        <v>-2.526047958182551</v>
+        <v>-2.820131346146331</v>
       </c>
       <c r="AF28">
-        <v>-0.07828553825921571</v>
+        <v>-0.2252527577988365</v>
       </c>
       <c r="AG28">
-        <v>-0.6264721947011245</v>
+        <v>0.9415770296083433</v>
       </c>
       <c r="AH28">
-        <v>-0.04317415052482479</v>
+        <v>-0.4130343592959618</v>
       </c>
       <c r="AI28">
         <v>-0.2487184825752398</v>
@@ -6301,19 +6301,19 @@
         <v>0.1305705688296778</v>
       </c>
       <c r="F29">
-        <v>-1.980020246958708</v>
+        <v>-2.400759392933219</v>
       </c>
       <c r="G29">
-        <v>3.276335353356722</v>
+        <v>2.84108769241589</v>
       </c>
       <c r="H29">
-        <v>0.5080004178327607</v>
+        <v>0.09120428510985919</v>
       </c>
       <c r="I29">
-        <v>-0.05170641987441976</v>
+        <v>-0.7173552233158824</v>
       </c>
       <c r="J29">
-        <v>2.570252841178055</v>
+        <v>2.544671430444016</v>
       </c>
       <c r="K29">
         <v>-4.017977562145742</v>
@@ -6373,19 +6373,19 @@
         <v>0.5007283442346501</v>
       </c>
       <c r="AD29">
-        <v>-1.310863192426792</v>
+        <v>-1.333731049315133</v>
       </c>
       <c r="AE29">
-        <v>0.6161275532960625</v>
+        <v>0.8092040066423187</v>
       </c>
       <c r="AF29">
-        <v>0.316817410845421</v>
+        <v>0.3797687312225661</v>
       </c>
       <c r="AG29">
-        <v>-0.4338463154299063</v>
+        <v>0.3236901533908606</v>
       </c>
       <c r="AH29">
-        <v>-0.142909654031498</v>
+        <v>-0.3631635066549022</v>
       </c>
       <c r="AI29">
         <v>-2.588707301629259</v>
@@ -6508,19 +6508,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F30">
-        <v>-0.2977939065118249</v>
+        <v>-0.5109540717986834</v>
       </c>
       <c r="G30">
-        <v>0.9253589583929829</v>
+        <v>0.8980995689466639</v>
       </c>
       <c r="H30">
-        <v>-0.5617354998996114</v>
+        <v>-0.5566758943823941</v>
       </c>
       <c r="I30">
-        <v>-0.5436065797643344</v>
+        <v>-0.3088325052654578</v>
       </c>
       <c r="J30">
-        <v>-0.8038284038777723</v>
+        <v>-0.9708743040708994</v>
       </c>
       <c r="K30">
         <v>1.433253659064836</v>
@@ -6580,19 +6580,19 @@
         <v>-0.3027106594859394</v>
       </c>
       <c r="AD30">
-        <v>0.4635711841393251</v>
+        <v>1.09369247035347</v>
       </c>
       <c r="AE30">
-        <v>1.113751773233083</v>
+        <v>1.096381873527114</v>
       </c>
       <c r="AF30">
-        <v>0.2755805284091946</v>
+        <v>0.2958492139870864</v>
       </c>
       <c r="AG30">
-        <v>0.009039440749233116</v>
+        <v>-0.7736542328101703</v>
       </c>
       <c r="AH30">
-        <v>-0.2019516766261939</v>
+        <v>-0.1938752808816665</v>
       </c>
       <c r="AI30">
         <v>-0.5311527305958956</v>
@@ -6715,19 +6715,19 @@
         <v>0.1320360290718905</v>
       </c>
       <c r="F31">
-        <v>0.6311532344334724</v>
+        <v>0.5083408277942773</v>
       </c>
       <c r="G31">
-        <v>0.3592640058742014</v>
+        <v>0.4575601523151877</v>
       </c>
       <c r="H31">
-        <v>-1.914372798683122</v>
+        <v>-1.807866705795726</v>
       </c>
       <c r="I31">
-        <v>-1.342930023485941</v>
+        <v>-1.113650584545407</v>
       </c>
       <c r="J31">
-        <v>-0.2771162169649992</v>
+        <v>-0.9163819372057486</v>
       </c>
       <c r="K31">
         <v>0.4854220800330602</v>
@@ -6787,19 +6787,19 @@
         <v>-0.1176610005361818</v>
       </c>
       <c r="AD31">
-        <v>2.081001495349428</v>
+        <v>2.844758649033861</v>
       </c>
       <c r="AE31">
-        <v>1.166498940606996</v>
+        <v>0.9676587269386518</v>
       </c>
       <c r="AF31">
-        <v>0.1563839540362648</v>
+        <v>0.002724001396237075</v>
       </c>
       <c r="AG31">
-        <v>0.4044951312099392</v>
+        <v>0.1868081323327374</v>
       </c>
       <c r="AH31">
-        <v>0.1303481118767193</v>
+        <v>0.4543283381628581</v>
       </c>
       <c r="AI31">
         <v>-0.6286266877204071</v>
@@ -6922,19 +6922,19 @@
         <v>0.08082045401489035</v>
       </c>
       <c r="F32">
-        <v>-1.56740497039669</v>
+        <v>-1.784847496028044</v>
       </c>
       <c r="G32">
-        <v>1.529079586820322</v>
+        <v>1.230614445158921</v>
       </c>
       <c r="H32">
-        <v>-0.7467611122349074</v>
+        <v>-0.8753959270631227</v>
       </c>
       <c r="I32">
-        <v>0.5881646765324703</v>
+        <v>0.7716623370794716</v>
       </c>
       <c r="J32">
-        <v>-1.237414127267997</v>
+        <v>-0.7646436795122542</v>
       </c>
       <c r="K32">
         <v>1.596658870799691</v>
@@ -6994,19 +6994,19 @@
         <v>-0.3122372026905569</v>
       </c>
       <c r="AD32">
-        <v>2.20949141053619</v>
+        <v>3.084079007597126</v>
       </c>
       <c r="AE32">
-        <v>2.254626304070345</v>
+        <v>2.018554358350786</v>
       </c>
       <c r="AF32">
-        <v>-0.6900635583289469</v>
+        <v>-0.9087265592844942</v>
       </c>
       <c r="AG32">
-        <v>-0.4019606764783178</v>
+        <v>0.5766812536840955</v>
       </c>
       <c r="AH32">
-        <v>-0.03989143667537205</v>
+        <v>-0.2630926631295377</v>
       </c>
       <c r="AI32">
         <v>-1.312930420219275</v>
@@ -7129,19 +7129,19 @@
         <v>0.1342342194352098</v>
       </c>
       <c r="F33">
-        <v>-0.5457671558375843</v>
+        <v>-0.4526824800546206</v>
       </c>
       <c r="G33">
-        <v>-0.2510535500074325</v>
+        <v>-0.3793746663693651</v>
       </c>
       <c r="H33">
-        <v>-1.133237566489232</v>
+        <v>-1.101800169210432</v>
       </c>
       <c r="I33">
-        <v>1.535237938391886</v>
+        <v>1.701685319382578</v>
       </c>
       <c r="J33">
-        <v>-0.9658836547169591</v>
+        <v>-0.479583242765153</v>
       </c>
       <c r="K33">
         <v>-4.424744070662588</v>
@@ -7201,19 +7201,19 @@
         <v>0.8685428754736342</v>
       </c>
       <c r="AD33">
-        <v>-2.95111462526845</v>
+        <v>-4.38663924062512</v>
       </c>
       <c r="AE33">
-        <v>-2.16029721098028</v>
+        <v>-1.932430802413792</v>
       </c>
       <c r="AF33">
-        <v>-0.5894876897519079</v>
+        <v>-0.3889604221425924</v>
       </c>
       <c r="AG33">
-        <v>1.362310153925946</v>
+        <v>-0.6859347055586822</v>
       </c>
       <c r="AH33">
-        <v>-0.09887814409766513</v>
+        <v>1.248793060844299</v>
       </c>
       <c r="AI33">
         <v>3.82885369643034</v>
@@ -7336,19 +7336,19 @@
         <v>-0.2695044109972272</v>
       </c>
       <c r="F34">
-        <v>1.953452427282499</v>
+        <v>2.332473369497436</v>
       </c>
       <c r="G34">
-        <v>-0.6470429154051638</v>
+        <v>-0.4906074587565096</v>
       </c>
       <c r="H34">
-        <v>0.6475747286190677</v>
+        <v>0.5766233161944156</v>
       </c>
       <c r="I34">
-        <v>-0.2665285542580233</v>
+        <v>-0.585879287831499</v>
       </c>
       <c r="J34">
-        <v>1.118990819595224</v>
+        <v>1.158333121467975</v>
       </c>
       <c r="K34">
         <v>4.91716444159387</v>
@@ -7408,19 +7408,19 @@
         <v>-0.1094231623074829</v>
       </c>
       <c r="AD34">
-        <v>-0.4594815019063576</v>
+        <v>-0.9042494843391056</v>
       </c>
       <c r="AE34">
-        <v>-1.798304127940896</v>
+        <v>-1.736655448610809</v>
       </c>
       <c r="AF34">
-        <v>0.3462781248294727</v>
+        <v>0.4405738826114068</v>
       </c>
       <c r="AG34">
-        <v>-0.2890093412400216</v>
+        <v>0.07551422214436018</v>
       </c>
       <c r="AH34">
-        <v>-0.06952444348053471</v>
+        <v>-0.2793633229684118</v>
       </c>
       <c r="AI34">
         <v>-1.372373196888318</v>
@@ -7543,19 +7543,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F35">
-        <v>-0.1363657164759434</v>
+        <v>-0.46400319170076</v>
       </c>
       <c r="G35">
-        <v>1.365960602690794</v>
+        <v>1.411457892503412</v>
       </c>
       <c r="H35">
-        <v>1.01056156291957</v>
+        <v>0.9582189676482979</v>
       </c>
       <c r="I35">
-        <v>0.5513060290180831</v>
+        <v>0.6168204934926242</v>
       </c>
       <c r="J35">
-        <v>-0.4850137493422474</v>
+        <v>-0.2467129904753848</v>
       </c>
       <c r="K35">
         <v>0.1629082988196737</v>
@@ -7615,19 +7615,19 @@
         <v>0.7063380757305133</v>
       </c>
       <c r="AD35">
-        <v>3.27834822974753</v>
+        <v>4.411618543005972</v>
       </c>
       <c r="AE35">
-        <v>1.740031836867948</v>
+        <v>1.384590447039082</v>
       </c>
       <c r="AF35">
-        <v>-0.2670664800890128</v>
+        <v>-0.4930348162495088</v>
       </c>
       <c r="AG35">
-        <v>0.1084401685819258</v>
+        <v>0.07693160420184167</v>
       </c>
       <c r="AH35">
-        <v>0.3708339872972807</v>
+        <v>0.1215162007427789</v>
       </c>
       <c r="AI35">
         <v>-0.06024653638840675</v>
@@ -7750,19 +7750,19 @@
         <v>0.1313032989507841</v>
       </c>
       <c r="F36">
-        <v>0.4545623172232885</v>
+        <v>0.8857899756007958</v>
       </c>
       <c r="G36">
-        <v>-1.225234278592479</v>
+        <v>-1.282290697912024</v>
       </c>
       <c r="H36">
-        <v>-0.2113803167704824</v>
+        <v>-0.2401836029394132</v>
       </c>
       <c r="I36">
-        <v>1.365225681522773</v>
+        <v>1.108794840995963</v>
       </c>
       <c r="J36">
-        <v>0.7691323420353381</v>
+        <v>1.152598437769841</v>
       </c>
       <c r="K36">
         <v>-0.9952103399213541</v>
@@ -7822,19 +7822,19 @@
         <v>0.08108771777601204</v>
       </c>
       <c r="AD36">
-        <v>-2.555599909096352</v>
+        <v>-3.27150617331539</v>
       </c>
       <c r="AE36">
-        <v>0.09534406808075468</v>
+        <v>0.31711416960794</v>
       </c>
       <c r="AF36">
-        <v>-0.06866681218048365</v>
+        <v>0.0123163089219902</v>
       </c>
       <c r="AG36">
-        <v>0.1267674298351988</v>
+        <v>-0.3812224754660203</v>
       </c>
       <c r="AH36">
-        <v>0.1270936914637735</v>
+        <v>0.03900579067278966</v>
       </c>
       <c r="AI36">
         <v>0.07450172633237688</v>
@@ -7957,19 +7957,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F37">
-        <v>-1.695562818408902</v>
+        <v>-1.5662871982809</v>
       </c>
       <c r="G37">
-        <v>-1.177504317991542</v>
+        <v>-1.381257699433706</v>
       </c>
       <c r="H37">
-        <v>-0.01773229839838623</v>
+        <v>0.04988229989725747</v>
       </c>
       <c r="I37">
-        <v>0.5651414800585901</v>
+        <v>0.8623649766233284</v>
       </c>
       <c r="J37">
-        <v>-1.563032319621478</v>
+        <v>-1.16994441785802</v>
       </c>
       <c r="K37">
         <v>-4.667902573532463</v>
@@ -8029,19 +8029,19 @@
         <v>0.460236557608709</v>
       </c>
       <c r="AD37">
-        <v>-2.83322385287683</v>
+        <v>-4.097568583811053</v>
       </c>
       <c r="AE37">
-        <v>-0.3972441443389783</v>
+        <v>-0.2144439764237613</v>
       </c>
       <c r="AF37">
-        <v>-0.3970639615258336</v>
+        <v>-0.3867012670493176</v>
       </c>
       <c r="AG37">
-        <v>1.074702538500204</v>
+        <v>-0.1393285741549294</v>
       </c>
       <c r="AH37">
-        <v>0.2365458868909258</v>
+        <v>1.077401808766686</v>
       </c>
       <c r="AI37">
         <v>1.658736825799218</v>
@@ -8164,19 +8164,19 @@
         <v>0.463230043811986</v>
       </c>
       <c r="F38">
-        <v>-0.4305801649955896</v>
+        <v>0.04574018377263044</v>
       </c>
       <c r="G38">
-        <v>-0.5168224425206518</v>
+        <v>-0.8012345529952991</v>
       </c>
       <c r="H38">
-        <v>0.4914047360483497</v>
+        <v>0.3048373801470263</v>
       </c>
       <c r="I38">
-        <v>0.4686424052738588</v>
+        <v>0.5040426463255665</v>
       </c>
       <c r="J38">
-        <v>-1.304517887011377</v>
+        <v>-0.3917216744093349</v>
       </c>
       <c r="K38">
         <v>-0.4096707574060942</v>
@@ -8236,19 +8236,19 @@
         <v>-0.7139474642365543</v>
       </c>
       <c r="AD38">
-        <v>2.9994041858856</v>
+        <v>3.904844597827371</v>
       </c>
       <c r="AE38">
-        <v>0.2728177967611435</v>
+        <v>-0.0926247322180791</v>
       </c>
       <c r="AF38">
-        <v>-1.945460969962853</v>
+        <v>-1.935953866855487</v>
       </c>
       <c r="AG38">
-        <v>-1.663604265993972</v>
+        <v>-0.6945371660480574</v>
       </c>
       <c r="AH38">
-        <v>-0.1315069766451107</v>
+        <v>-1.863138092414004</v>
       </c>
       <c r="AI38">
         <v>-1.618848481795294</v>
@@ -8371,19 +8371,19 @@
         <v>-0.1734915543477418</v>
       </c>
       <c r="F39">
-        <v>0.4222122626689951</v>
+        <v>0.409160262761813</v>
       </c>
       <c r="G39">
-        <v>-0.6107710622258953</v>
+        <v>-0.4799028830555282</v>
       </c>
       <c r="H39">
-        <v>-0.6598718140173243</v>
+        <v>-0.5281766966799541</v>
       </c>
       <c r="I39">
-        <v>-1.298946595367539</v>
+        <v>-1.176653686090065</v>
       </c>
       <c r="J39">
-        <v>0.1049860403969301</v>
+        <v>-0.509905082919403</v>
       </c>
       <c r="K39">
         <v>0.4266015886596937</v>
@@ -8443,19 +8443,19 @@
         <v>0.195890920168838</v>
       </c>
       <c r="AD39">
-        <v>1.30777563836203</v>
+        <v>1.660186226980185</v>
       </c>
       <c r="AE39">
-        <v>1.341899030497336</v>
+        <v>1.142226499160542</v>
       </c>
       <c r="AF39">
-        <v>-1.383012167542606</v>
+        <v>-1.498785566576443</v>
       </c>
       <c r="AG39">
-        <v>0.05877515548255657</v>
+        <v>-0.1432052036883608</v>
       </c>
       <c r="AH39">
-        <v>-0.2656846569019804</v>
+        <v>0.04340259292351316</v>
       </c>
       <c r="AI39">
         <v>-0.4451581446607135</v>
@@ -8578,19 +8578,19 @@
         <v>0.1349669495563162</v>
       </c>
       <c r="F40">
-        <v>0.1325799175405022</v>
+        <v>-0.3752207015222777</v>
       </c>
       <c r="G40">
-        <v>3.002223353072304</v>
+        <v>2.981062568035953</v>
       </c>
       <c r="H40">
-        <v>-0.6868565622996844</v>
+        <v>-0.8131717817944391</v>
       </c>
       <c r="I40">
-        <v>0.01115939311716622</v>
+        <v>0.2210655513497004</v>
       </c>
       <c r="J40">
-        <v>-1.094696830096989</v>
+        <v>-0.8960221043690515</v>
       </c>
       <c r="K40">
         <v>2.475471132281606</v>
@@ -8650,19 +8650,19 @@
         <v>0.2781900784144161</v>
       </c>
       <c r="AD40">
-        <v>1.735510934769253</v>
+        <v>2.534355961354152</v>
       </c>
       <c r="AE40">
-        <v>0.3071721023463315</v>
+        <v>0.2009323841802795</v>
       </c>
       <c r="AF40">
-        <v>0.6419923850112996</v>
+        <v>0.6078134073559622</v>
       </c>
       <c r="AG40">
-        <v>-0.4953370260038868</v>
+        <v>0.2003214449297301</v>
       </c>
       <c r="AH40">
-        <v>0.2568276691017291</v>
+        <v>-0.4705633425635519</v>
       </c>
       <c r="AI40">
         <v>-0.2553380248312295</v>
@@ -8785,19 +8785,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F41">
-        <v>-0.5272903394525239</v>
+        <v>-0.7675700618533364</v>
       </c>
       <c r="G41">
-        <v>0.4654711310086961</v>
+        <v>0.5287272525025062</v>
       </c>
       <c r="H41">
-        <v>2.548492046230358</v>
+        <v>2.514609895637651</v>
       </c>
       <c r="I41">
-        <v>-0.5873309068637097</v>
+        <v>-0.4976550764286256</v>
       </c>
       <c r="J41">
-        <v>-0.6150283100824155</v>
+        <v>-0.5398852203370403</v>
       </c>
       <c r="K41">
         <v>0.5908039408607256</v>
@@ -8857,19 +8857,19 @@
         <v>-0.7470249345853431</v>
       </c>
       <c r="AD41">
-        <v>0.827486415513251</v>
+        <v>1.356043018299028</v>
       </c>
       <c r="AE41">
-        <v>1.123774894862972</v>
+        <v>1.064257623254456</v>
       </c>
       <c r="AF41">
-        <v>-0.1007226953256334</v>
+        <v>-0.1524133820448652</v>
       </c>
       <c r="AG41">
-        <v>0.0962618042252603</v>
+        <v>0.1351043045262304</v>
       </c>
       <c r="AH41">
-        <v>-0.002415271807903586</v>
+        <v>0.1328428847241309</v>
       </c>
       <c r="AI41">
         <v>-0.2541022468668835</v>
@@ -8992,19 +8992,19 @@
         <v>-0.2511028273729498</v>
       </c>
       <c r="F42">
-        <v>2.90322278972689</v>
+        <v>2.833346819076852</v>
       </c>
       <c r="G42">
-        <v>-0.6370926047573731</v>
+        <v>-0.08275983759893768</v>
       </c>
       <c r="H42">
-        <v>-0.7994495607957699</v>
+        <v>-0.5354555589395471</v>
       </c>
       <c r="I42">
-        <v>0.2680177123966903</v>
+        <v>0.2844647426827752</v>
       </c>
       <c r="J42">
-        <v>0.6950959078889376</v>
+        <v>0.2104169169487169</v>
       </c>
       <c r="K42">
         <v>2.950653071481629</v>
@@ -9064,19 +9064,19 @@
         <v>-0.06827248395569858</v>
       </c>
       <c r="AD42">
-        <v>1.922926373161737</v>
+        <v>2.216287900430873</v>
       </c>
       <c r="AE42">
-        <v>-1.768442630322928</v>
+        <v>-1.950658814471511</v>
       </c>
       <c r="AF42">
-        <v>-0.2395625147352812</v>
+        <v>-0.159861364016179</v>
       </c>
       <c r="AG42">
-        <v>-0.1629303652681401</v>
+        <v>-0.3513640782869243</v>
       </c>
       <c r="AH42">
-        <v>0.05672339632986626</v>
+        <v>-0.2501717108511523</v>
       </c>
       <c r="AI42">
         <v>-0.943127331745513</v>
@@ -9199,19 +9199,19 @@
         <v>0.1327687591929969</v>
       </c>
       <c r="F43">
-        <v>-1.493554205553412</v>
+        <v>-1.381279202983619</v>
       </c>
       <c r="G43">
-        <v>-1.426593741389257</v>
+        <v>-1.528065692659512</v>
       </c>
       <c r="H43">
-        <v>1.636114636129222</v>
+        <v>1.699380643664956</v>
       </c>
       <c r="I43">
-        <v>-0.8018380920113358</v>
+        <v>-0.5436568923015042</v>
       </c>
       <c r="J43">
-        <v>-1.238530537756243</v>
+        <v>-1.205436896272279</v>
       </c>
       <c r="K43">
         <v>-6.47919097483534</v>
@@ -9271,19 +9271,19 @@
         <v>1.168750758876079</v>
       </c>
       <c r="AD43">
-        <v>-2.396047543566431</v>
+        <v>-3.189796780830663</v>
       </c>
       <c r="AE43">
-        <v>-0.5469913575817961</v>
+        <v>-0.2895307466778606</v>
       </c>
       <c r="AF43">
-        <v>0.1551111498172837</v>
+        <v>0.2296850959818426</v>
       </c>
       <c r="AG43">
-        <v>-0.9373470740438355</v>
+        <v>0.7382737831596978</v>
       </c>
       <c r="AH43">
-        <v>-0.1060942931340973</v>
+        <v>-0.7738213105475799</v>
       </c>
       <c r="AI43">
         <v>-0.9605558091027551</v>
@@ -9406,19 +9406,19 @@
         <v>0.6527611096163264</v>
       </c>
       <c r="F44">
-        <v>-0.08295083368889461</v>
+        <v>0.1482908028368977</v>
       </c>
       <c r="G44">
-        <v>-2.608935113672662</v>
+        <v>-2.44460790672541</v>
       </c>
       <c r="H44">
-        <v>1.271062720789645</v>
+        <v>1.470339071628516</v>
       </c>
       <c r="I44">
-        <v>-3.757802244089647</v>
+        <v>-3.59134234372091</v>
       </c>
       <c r="J44">
-        <v>0.0986804471776665</v>
+        <v>-1.034418669959248</v>
       </c>
       <c r="K44">
         <v>2.287408448830479</v>
@@ -9478,19 +9478,19 @@
         <v>0.3416018551796846</v>
       </c>
       <c r="AD44">
-        <v>0.1976175807969054</v>
+        <v>-0.1858275454569238</v>
       </c>
       <c r="AE44">
-        <v>-2.03448476049363</v>
+        <v>-2.072399698889962</v>
       </c>
       <c r="AF44">
-        <v>-0.156296086544685</v>
+        <v>-0.07287110558425108</v>
       </c>
       <c r="AG44">
-        <v>-0.827205916094831</v>
+        <v>0.03326675672849458</v>
       </c>
       <c r="AH44">
-        <v>0.1562491808293493</v>
+        <v>-0.8376953002161641</v>
       </c>
       <c r="AI44">
         <v>-0.5797154321736138</v>
@@ -9613,19 +9613,19 @@
         <v>-0.5913948964631766</v>
       </c>
       <c r="F45">
-        <v>0.5920313062201294</v>
+        <v>0.4152777864638258</v>
       </c>
       <c r="G45">
-        <v>0.2149352652687446</v>
+        <v>0.4170084503153166</v>
       </c>
       <c r="H45">
-        <v>1.140608721205443</v>
+        <v>1.20224732312535</v>
       </c>
       <c r="I45">
-        <v>-0.3491851082249448</v>
+        <v>-0.1971325579109738</v>
       </c>
       <c r="J45">
-        <v>-0.607693026312887</v>
+        <v>-0.6580006760912253</v>
       </c>
       <c r="K45">
         <v>3.316816692350613</v>
@@ -9685,19 +9685,19 @@
         <v>-0.1754066668331659</v>
       </c>
       <c r="AD45">
-        <v>2.903739579113998</v>
+        <v>4.247828573538622</v>
       </c>
       <c r="AE45">
-        <v>1.52572996460832</v>
+        <v>1.262504891890129</v>
       </c>
       <c r="AF45">
-        <v>0.1495205606079606</v>
+        <v>0.05153006715507558</v>
       </c>
       <c r="AG45">
-        <v>-0.6414155856166776</v>
+        <v>-0.466234291188752</v>
       </c>
       <c r="AH45">
-        <v>-0.3508226535246008</v>
+        <v>-0.7949310736688199</v>
       </c>
       <c r="AI45">
         <v>-1.759512769045634</v>
@@ -9820,19 +9820,19 @@
         <v>0.836918719860325</v>
       </c>
       <c r="F46">
-        <v>-2.480173458843234</v>
+        <v>-2.090904842724254</v>
       </c>
       <c r="G46">
-        <v>-1.519071037261191</v>
+        <v>-1.993127579985964</v>
       </c>
       <c r="H46">
-        <v>-0.9306234767737344</v>
+        <v>-0.9893314199031329</v>
       </c>
       <c r="I46">
-        <v>-0.08384344556322514</v>
+        <v>-0.1539738191996654</v>
       </c>
       <c r="J46">
-        <v>0.175204010492098</v>
+        <v>0.2383841155333191</v>
       </c>
       <c r="K46">
         <v>-4.716575900164394</v>
@@ -9892,19 +9892,19 @@
         <v>0.3690303122730947</v>
       </c>
       <c r="AD46">
-        <v>-3.190476543692534</v>
+        <v>-4.32261427781793</v>
       </c>
       <c r="AE46">
-        <v>0.04107351169153742</v>
+        <v>0.2794669631485705</v>
       </c>
       <c r="AF46">
-        <v>-0.6030899287053682</v>
+        <v>-0.5448939569023288</v>
       </c>
       <c r="AG46">
-        <v>0.1088929113565984</v>
+        <v>-0.2502516826736738</v>
       </c>
       <c r="AH46">
-        <v>-0.005337487504505875</v>
+        <v>0.06277108366753589</v>
       </c>
       <c r="AI46">
         <v>1.394872185388937</v>
@@ -10027,19 +10027,19 @@
         <v>-0.1748532940305042</v>
       </c>
       <c r="F47">
-        <v>2.587441334474506</v>
+        <v>2.216154402304308</v>
       </c>
       <c r="G47">
-        <v>1.076040907478348</v>
+        <v>1.585362894848891</v>
       </c>
       <c r="H47">
-        <v>0.07220318886746852</v>
+        <v>0.20205246147111</v>
       </c>
       <c r="I47">
-        <v>1.466891917704198</v>
+        <v>1.351294474675134</v>
       </c>
       <c r="J47">
-        <v>0.8876693696310842</v>
+        <v>0.8063507914099076</v>
       </c>
       <c r="K47">
         <v>3.994751297689533</v>
@@ -10099,19 +10099,19 @@
         <v>-0.2053759456103822</v>
       </c>
       <c r="AD47">
-        <v>-0.7129478507590424</v>
+        <v>-1.508180638823074</v>
       </c>
       <c r="AE47">
-        <v>-1.821304897588436</v>
+        <v>-1.773031686805856</v>
       </c>
       <c r="AF47">
-        <v>-0.2630257228200817</v>
+        <v>-0.2015070994417013</v>
       </c>
       <c r="AG47">
-        <v>1.241622209593683</v>
+        <v>0.1138688338048358</v>
       </c>
       <c r="AH47">
-        <v>-0.2451313172291464</v>
+        <v>1.318705733580973</v>
       </c>
       <c r="AI47">
         <v>-0.3354468523601962</v>
@@ -10234,19 +10234,19 @@
         <v>-0.1916384014992065</v>
       </c>
       <c r="F48">
-        <v>3.835637833518924</v>
+        <v>4.336210602931201</v>
       </c>
       <c r="G48">
-        <v>-0.7344246960078704</v>
+        <v>-0.3728905252854994</v>
       </c>
       <c r="H48">
-        <v>-0.6149907052582179</v>
+        <v>-0.6285606154746386</v>
       </c>
       <c r="I48">
-        <v>0.2671971811523407</v>
+        <v>-0.1281042095862382</v>
       </c>
       <c r="J48">
-        <v>1.576059074922017</v>
+        <v>1.599256675478977</v>
       </c>
       <c r="K48">
         <v>6.687454227331093</v>
@@ -10306,19 +10306,19 @@
         <v>0.05860094422200399</v>
       </c>
       <c r="AD48">
-        <v>3.926788945314459</v>
+        <v>3.848504778651483</v>
       </c>
       <c r="AE48">
-        <v>-2.851367570334796</v>
+        <v>-3.306896699740447</v>
       </c>
       <c r="AF48">
-        <v>0.351061025935975</v>
+        <v>0.1077109458871434</v>
       </c>
       <c r="AG48">
-        <v>-0.6763707122906584</v>
+        <v>1.182270447598903</v>
       </c>
       <c r="AH48">
-        <v>0.1144438994268681</v>
+        <v>-0.4155344224014735</v>
       </c>
       <c r="AI48">
         <v>-0.9662416305735366</v>
@@ -10441,19 +10441,19 @@
         <v>-0.101660297563713</v>
       </c>
       <c r="F49">
-        <v>-0.09653691856878488</v>
+        <v>-0.3704956879410636</v>
       </c>
       <c r="G49">
-        <v>0.9462916141053307</v>
+        <v>1.015502216450743</v>
       </c>
       <c r="H49">
-        <v>1.064207974349252</v>
+        <v>1.051536668840506</v>
       </c>
       <c r="I49">
-        <v>-0.3019661347496588</v>
+        <v>-0.04294762960476543</v>
       </c>
       <c r="J49">
-        <v>-1.415912171917973</v>
+        <v>-1.17348324605912</v>
       </c>
       <c r="K49">
         <v>2.732462993541611</v>
@@ -10513,19 +10513,19 @@
         <v>-0.412546909115466</v>
       </c>
       <c r="AD49">
-        <v>2.648005512536512</v>
+        <v>3.673586491778142</v>
       </c>
       <c r="AE49">
-        <v>0.4641784820049322</v>
+        <v>0.2442777486062649</v>
       </c>
       <c r="AF49">
-        <v>0.01306892812614335</v>
+        <v>-0.0181421046392678</v>
       </c>
       <c r="AG49">
-        <v>0.7863259984752653</v>
+        <v>-0.3184185452052744</v>
       </c>
       <c r="AH49">
-        <v>-0.1328011205917168</v>
+        <v>0.7247883457185321</v>
       </c>
       <c r="AI49">
         <v>-0.142881430660114</v>
@@ -10648,19 +10648,19 @@
         <v>0.9182445342181839</v>
       </c>
       <c r="F50">
-        <v>-0.002715005747397553</v>
+        <v>-0.03364458785539194</v>
       </c>
       <c r="G50">
-        <v>-0.7769198469199292</v>
+        <v>-0.653752513278271</v>
       </c>
       <c r="H50">
-        <v>0.5434731893468417</v>
+        <v>0.6751882513444432</v>
       </c>
       <c r="I50">
-        <v>-0.07779517561473845</v>
+        <v>0.1103032628231024</v>
       </c>
       <c r="J50">
-        <v>-0.5741574500727007</v>
+        <v>-0.7002438623854595</v>
       </c>
       <c r="K50">
         <v>-0.1395405892638965</v>
@@ -10720,19 +10720,19 @@
         <v>0.4548437450286327</v>
       </c>
       <c r="AD50">
-        <v>-1.760390688584983</v>
+        <v>-2.101787205774819</v>
       </c>
       <c r="AE50">
-        <v>0.6959065947375164</v>
+        <v>0.9151622255602314</v>
       </c>
       <c r="AF50">
-        <v>0.5792674205373501</v>
+        <v>0.5547725543524276</v>
       </c>
       <c r="AG50">
-        <v>-0.1884148875062159</v>
+        <v>0.9948866788351272</v>
       </c>
       <c r="AH50">
-        <v>0.2186456310683823</v>
+        <v>0.0516129051779923</v>
       </c>
       <c r="AI50">
         <v>-1.103012429580609</v>
@@ -10855,19 +10855,19 @@
         <v>0.1171820044112727</v>
       </c>
       <c r="F51">
-        <v>-0.125588702339547</v>
+        <v>0.2075555411665304</v>
       </c>
       <c r="G51">
-        <v>-3.064958499233619</v>
+        <v>-2.927253077443043</v>
       </c>
       <c r="H51">
-        <v>-0.02815076241938808</v>
+        <v>0.2788726579451614</v>
       </c>
       <c r="I51">
-        <v>-0.5976816463083223</v>
+        <v>-0.2728815137791177</v>
       </c>
       <c r="J51">
-        <v>-0.638876329129455</v>
+        <v>-1.178087229168236</v>
       </c>
       <c r="K51">
         <v>5.340184314125739</v>
@@ -10927,19 +10927,19 @@
         <v>-0.1520092919458262</v>
       </c>
       <c r="AD51">
-        <v>-0.7081548791108389</v>
+        <v>-0.5067197403507991</v>
       </c>
       <c r="AE51">
-        <v>0.4428832616476817</v>
+        <v>0.5308113220257983</v>
       </c>
       <c r="AF51">
-        <v>0.5725377860074997</v>
+        <v>0.6642203576124247</v>
       </c>
       <c r="AG51">
-        <v>0.6579344038821949</v>
+        <v>-1.100763246509132</v>
       </c>
       <c r="AH51">
-        <v>0.1405432090290592</v>
+        <v>0.3877802295272662</v>
       </c>
       <c r="AI51">
         <v>-1.405452112130976</v>
@@ -11062,19 +11062,19 @@
         <v>-0.7316950548012814</v>
       </c>
       <c r="F52">
-        <v>2.125777835264417</v>
+        <v>2.031573956257174</v>
       </c>
       <c r="G52">
-        <v>-0.941667421988358</v>
+        <v>-0.4347984329975788</v>
       </c>
       <c r="H52">
-        <v>0.3179490564222468</v>
+        <v>0.5839616387485372</v>
       </c>
       <c r="I52">
-        <v>-0.09629699886193718</v>
+        <v>0.003899384043846141</v>
       </c>
       <c r="J52">
-        <v>0.2814507142224854</v>
+        <v>-0.20934315093</v>
       </c>
       <c r="K52">
         <v>3.274246933618093</v>
@@ -11134,19 +11134,19 @@
         <v>-0.3032028750958755</v>
       </c>
       <c r="AD52">
-        <v>1.363529877667301</v>
+        <v>1.375429749464558</v>
       </c>
       <c r="AE52">
-        <v>-2.208619900650269</v>
+        <v>-2.332718896991488</v>
       </c>
       <c r="AF52">
-        <v>0.1400399418375833</v>
+        <v>0.2183678342841899</v>
       </c>
       <c r="AG52">
-        <v>-0.3465412465896867</v>
+        <v>-0.0584809621660914</v>
       </c>
       <c r="AH52">
-        <v>0.02154745598600805</v>
+        <v>-0.3739614796441755</v>
       </c>
       <c r="AI52">
         <v>0.3496920273084612</v>
@@ -11269,19 +11269,19 @@
         <v>0.01806106038494543</v>
       </c>
       <c r="F53">
-        <v>1.359374722984867</v>
+        <v>1.207593978383835</v>
       </c>
       <c r="G53">
-        <v>-0.5184009437548988</v>
+        <v>-0.1216115720883633</v>
       </c>
       <c r="H53">
-        <v>1.653485308021829</v>
+        <v>1.808328473040988</v>
       </c>
       <c r="I53">
-        <v>1.777944147197805</v>
+        <v>1.724144255873164</v>
       </c>
       <c r="J53">
-        <v>0.1096532887730846</v>
+        <v>0.4665981460110319</v>
       </c>
       <c r="K53">
         <v>1.397345871994117</v>
@@ -11341,19 +11341,19 @@
         <v>-0.3415870880350247</v>
       </c>
       <c r="AD53">
-        <v>2.292416840755966</v>
+        <v>3.192511698254898</v>
       </c>
       <c r="AE53">
-        <v>0.7810923825668672</v>
+        <v>0.572078540522251</v>
       </c>
       <c r="AF53">
-        <v>-0.4758871610522114</v>
+        <v>-0.5111210515082545</v>
       </c>
       <c r="AG53">
-        <v>0.6455394760245757</v>
+        <v>-0.5336449326097135</v>
       </c>
       <c r="AH53">
-        <v>-0.1093751699311094</v>
+        <v>0.5410287436586124</v>
       </c>
       <c r="AI53">
         <v>1.188914629355687</v>
@@ -11476,19 +11476,19 @@
         <v>0.1378978700407418</v>
       </c>
       <c r="F54">
-        <v>-0.566399024007632</v>
+        <v>-0.8008052078502734</v>
       </c>
       <c r="G54">
-        <v>1.11352023928285</v>
+        <v>1.04716281504884</v>
       </c>
       <c r="H54">
-        <v>0.360592176215264</v>
+        <v>0.2886813763209112</v>
       </c>
       <c r="I54">
-        <v>-0.00778195061055119</v>
+        <v>0.06722620458283424</v>
       </c>
       <c r="J54">
-        <v>-0.5676096968437425</v>
+        <v>-0.3739617921787141</v>
       </c>
       <c r="K54">
         <v>-2.27445899900286</v>
@@ -11548,19 +11548,19 @@
         <v>0.9168542828359302</v>
       </c>
       <c r="AD54">
-        <v>0.1443052756080432</v>
+        <v>0.2265787494111656</v>
       </c>
       <c r="AE54">
-        <v>1.075385690750195</v>
+        <v>1.01086369358139</v>
       </c>
       <c r="AF54">
-        <v>-0.7948803443783723</v>
+        <v>-0.8603006434001942</v>
       </c>
       <c r="AG54">
-        <v>0.2487910812255754</v>
+        <v>-0.217369030615503</v>
       </c>
       <c r="AH54">
-        <v>0.1940377771849583</v>
+        <v>0.2157831632651413</v>
       </c>
       <c r="AI54">
         <v>-0.4944576428541265</v>
@@ -11683,19 +11683,19 @@
         <v>-0.08788721923362208</v>
       </c>
       <c r="F55">
-        <v>-0.387459949435929</v>
+        <v>-0.4474732224013402</v>
       </c>
       <c r="G55">
-        <v>-0.08068743532755907</v>
+        <v>-0.08214944059789586</v>
       </c>
       <c r="H55">
-        <v>2.066600215090343</v>
+        <v>1.927588328178805</v>
       </c>
       <c r="I55">
-        <v>0.7506692472710655</v>
+        <v>-0.1813756706788446</v>
       </c>
       <c r="J55">
-        <v>3.933024593730223</v>
+        <v>3.817714771062159</v>
       </c>
       <c r="K55">
         <v>-1.064909374742897</v>
@@ -11755,19 +11755,19 @@
         <v>0.1102235582253503</v>
       </c>
       <c r="AD55">
-        <v>-0.008508982509760843</v>
+        <v>0.02138827306763136</v>
       </c>
       <c r="AE55">
-        <v>-1.882830096399324</v>
+        <v>-1.807057302101448</v>
       </c>
       <c r="AF55">
-        <v>0.9481674466638006</v>
+        <v>1.133394051849771</v>
       </c>
       <c r="AG55">
-        <v>-0.07933876016272648</v>
+        <v>-0.6320637311398143</v>
       </c>
       <c r="AH55">
-        <v>-0.2632608939386458</v>
+        <v>-0.2507702120243689</v>
       </c>
       <c r="AI55">
         <v>2.253578252221951</v>
@@ -11890,19 +11890,19 @@
         <v>-0.2749851830285506</v>
       </c>
       <c r="F56">
-        <v>1.810482405964905</v>
+        <v>1.717334271935392</v>
       </c>
       <c r="G56">
-        <v>-0.5832600432555763</v>
+        <v>-0.1627479328124106</v>
       </c>
       <c r="H56">
-        <v>0.777859263960368</v>
+        <v>0.9493741408022084</v>
       </c>
       <c r="I56">
-        <v>0.1030800628979003</v>
+        <v>0.07377525738886653</v>
       </c>
       <c r="J56">
-        <v>0.4894406636476153</v>
+        <v>0.2405004540381146</v>
       </c>
       <c r="K56">
         <v>2.847689682117245</v>
@@ -11962,19 +11962,19 @@
         <v>-0.1022727716210243</v>
       </c>
       <c r="AD56">
-        <v>2.21437537560753</v>
+        <v>2.528633341027191</v>
       </c>
       <c r="AE56">
-        <v>-1.242429605989442</v>
+        <v>-1.502383018345449</v>
       </c>
       <c r="AF56">
-        <v>-0.5665966590574996</v>
+        <v>-0.55583772806834</v>
       </c>
       <c r="AG56">
-        <v>0.03304864709083198</v>
+        <v>-0.4756972776084102</v>
       </c>
       <c r="AH56">
-        <v>0.0262599162305184</v>
+        <v>-0.08263928061264564</v>
       </c>
       <c r="AI56">
         <v>-0.7799836928244315</v>
@@ -12097,19 +12097,19 @@
         <v>0.08985038793355372</v>
       </c>
       <c r="F57">
-        <v>1.891925110234598</v>
+        <v>1.886056239389541</v>
       </c>
       <c r="G57">
-        <v>-0.9806170050021581</v>
+        <v>-0.5976203064984604</v>
       </c>
       <c r="H57">
-        <v>-1.577065233734025</v>
+        <v>-1.302026459206084</v>
       </c>
       <c r="I57">
-        <v>-0.3437500828724284</v>
+        <v>-0.1754835525392062</v>
       </c>
       <c r="J57">
-        <v>0.1561787047092739</v>
+        <v>-0.4565321746181136</v>
       </c>
       <c r="K57">
         <v>2.328221425618853</v>
@@ -12169,19 +12169,19 @@
         <v>0.9511989915337162</v>
       </c>
       <c r="AD57">
-        <v>1.145802090875085</v>
+        <v>2.177990804057972</v>
       </c>
       <c r="AE57">
-        <v>-0.3257682345496168</v>
+        <v>-0.3002526775552953</v>
       </c>
       <c r="AF57">
-        <v>1.053974341526671</v>
+        <v>1.250404619176445</v>
       </c>
       <c r="AG57">
-        <v>-0.05658848165684129</v>
+        <v>-1.045972693506399</v>
       </c>
       <c r="AH57">
-        <v>-0.1901761297329304</v>
+        <v>-0.3318889487109352</v>
       </c>
       <c r="AI57">
         <v>-0.4616807592226515</v>
@@ -12304,19 +12304,19 @@
         <v>0.2896206390619916</v>
       </c>
       <c r="F58">
-        <v>0.03071897581346719</v>
+        <v>-0.06282564949874382</v>
       </c>
       <c r="G58">
-        <v>-0.4866027314387584</v>
+        <v>-0.3465837894358655</v>
       </c>
       <c r="H58">
-        <v>0.5928371252551898</v>
+        <v>0.7341309958511141</v>
       </c>
       <c r="I58">
-        <v>-1.564271390459851</v>
+        <v>-1.146147218472271</v>
       </c>
       <c r="J58">
-        <v>-1.351278707580058</v>
+        <v>-1.803356876700126</v>
       </c>
       <c r="K58">
         <v>3.912121557756062</v>
@@ -12376,19 +12376,19 @@
         <v>-0.09236585511892936</v>
       </c>
       <c r="AD58">
-        <v>2.199882115916258</v>
+        <v>3.357285499508679</v>
       </c>
       <c r="AE58">
-        <v>0.7930268288066217</v>
+        <v>0.6414283640056875</v>
       </c>
       <c r="AF58">
-        <v>0.5651552150937031</v>
+        <v>0.5615453771717078</v>
       </c>
       <c r="AG58">
-        <v>0.2986489507824257</v>
+        <v>-0.5921202398994565</v>
       </c>
       <c r="AH58">
-        <v>0.01667899460798721</v>
+        <v>0.1444591799703369</v>
       </c>
       <c r="AI58">
         <v>1.949800249652958</v>
@@ -12511,19 +12511,19 @@
         <v>-0.1746303196922418</v>
       </c>
       <c r="F59">
-        <v>2.131834354716875</v>
+        <v>2.351430594262353</v>
       </c>
       <c r="G59">
-        <v>-3.552171653349823</v>
+        <v>-2.913792064826454</v>
       </c>
       <c r="H59">
-        <v>1.617566619639654</v>
+        <v>2.051966059483596</v>
       </c>
       <c r="I59">
-        <v>-0.45765948099681</v>
+        <v>-0.3632969532228357</v>
       </c>
       <c r="J59">
-        <v>0.3564347166578511</v>
+        <v>-0.2169749191435487</v>
       </c>
       <c r="K59">
         <v>0.4210930319584552</v>
@@ -12583,19 +12583,19 @@
         <v>-1.165519719943915</v>
       </c>
       <c r="AD59">
-        <v>1.13126282429313</v>
+        <v>1.523762910942362</v>
       </c>
       <c r="AE59">
-        <v>0.8030684749516006</v>
+        <v>0.7145315285603651</v>
       </c>
       <c r="AF59">
-        <v>0.9368135498529445</v>
+        <v>0.760803562160811</v>
       </c>
       <c r="AG59">
-        <v>-0.2774228806750972</v>
+        <v>0.766227234300059</v>
       </c>
       <c r="AH59">
-        <v>-0.1088541716335317</v>
+        <v>-0.1192603997563355</v>
       </c>
       <c r="AI59">
         <v>1.37156656794702</v>
@@ -12718,19 +12718,19 @@
         <v>-0.03723263224000046</v>
       </c>
       <c r="F60">
-        <v>2.489736463593748</v>
+        <v>2.762001355534941</v>
       </c>
       <c r="G60">
-        <v>-0.8319659161858137</v>
+        <v>-0.5178779564113216</v>
       </c>
       <c r="H60">
-        <v>-0.01795943959016542</v>
+        <v>0.03883417107896982</v>
       </c>
       <c r="I60">
-        <v>-0.1216007608321208</v>
+        <v>-0.3161907374962525</v>
       </c>
       <c r="J60">
-        <v>0.8778651927286809</v>
+        <v>0.780112847063133</v>
       </c>
       <c r="K60">
         <v>3.407460738406218</v>
@@ -12790,19 +12790,19 @@
         <v>0.3725590948111014</v>
       </c>
       <c r="AD60">
-        <v>1.809411086706564</v>
+        <v>0.4680022880209668</v>
       </c>
       <c r="AE60">
-        <v>-2.017643566205205</v>
+        <v>-2.407232056989506</v>
       </c>
       <c r="AF60">
-        <v>0.1166571752621642</v>
+        <v>-0.3873111022198142</v>
       </c>
       <c r="AG60">
-        <v>-0.3888819456643019</v>
+        <v>2.218646883299312</v>
       </c>
       <c r="AH60">
-        <v>0.306849344425015</v>
+        <v>0.1340507243633816</v>
       </c>
       <c r="AI60">
         <v>0.06350481918872813</v>
@@ -12925,19 +12925,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F61">
-        <v>-1.547758960654344</v>
+        <v>-1.807342626917575</v>
       </c>
       <c r="G61">
-        <v>2.007720711823172</v>
+        <v>1.686850476237424</v>
       </c>
       <c r="H61">
-        <v>0.1322189467719539</v>
+        <v>-0.1232021554816705</v>
       </c>
       <c r="I61">
-        <v>-0.9294834464825018</v>
+        <v>-1.127157625154539</v>
       </c>
       <c r="J61">
-        <v>0.5638206108494389</v>
+        <v>0.5513227398930208</v>
       </c>
       <c r="K61">
         <v>-3.618057753434718</v>
@@ -12997,19 +12997,19 @@
         <v>1.774553853971518</v>
       </c>
       <c r="AD61">
-        <v>-1.468253337150532</v>
+        <v>-1.627653500463413</v>
       </c>
       <c r="AE61">
-        <v>1.047531896898536</v>
+        <v>1.190000319346199</v>
       </c>
       <c r="AF61">
-        <v>-0.1174873692004088</v>
+        <v>-0.09886519144747613</v>
       </c>
       <c r="AG61">
-        <v>-0.2215757633698951</v>
+        <v>-0.08712665098481405</v>
       </c>
       <c r="AH61">
-        <v>-0.1262193629361317</v>
+        <v>-0.2478917274513411</v>
       </c>
       <c r="AI61">
         <v>-2.005742041936404</v>
@@ -13132,19 +13132,19 @@
         <v>-0.1431059974568705</v>
       </c>
       <c r="F62">
-        <v>-0.05032599810408053</v>
+        <v>-0.1132525125080392</v>
       </c>
       <c r="G62">
-        <v>0.2697599961107268</v>
+        <v>0.2391614207647963</v>
       </c>
       <c r="H62">
-        <v>-1.388572589499197</v>
+        <v>-1.363793410616594</v>
       </c>
       <c r="I62">
-        <v>-1.282551821383173</v>
+        <v>-1.225568698600071</v>
       </c>
       <c r="J62">
-        <v>0.2572931042233182</v>
+        <v>-0.2823875962878857</v>
       </c>
       <c r="K62">
         <v>2.493525389554841</v>
@@ -13204,19 +13204,19 @@
         <v>-0.4790850959816138</v>
       </c>
       <c r="AD62">
-        <v>2.202925493300226</v>
+        <v>2.623771727341876</v>
       </c>
       <c r="AE62">
-        <v>1.608672263124453</v>
+        <v>1.327829134196289</v>
       </c>
       <c r="AF62">
-        <v>-0.6201156192113326</v>
+        <v>-0.9265358740671551</v>
       </c>
       <c r="AG62">
-        <v>0.2257511411508985</v>
+        <v>1.073815677772898</v>
       </c>
       <c r="AH62">
-        <v>0.2760534665148936</v>
+        <v>0.5038341490504414</v>
       </c>
       <c r="AI62">
         <v>-1.674109526489327</v>
@@ -13339,19 +13339,19 @@
         <v>0.2693206749586879</v>
       </c>
       <c r="F63">
-        <v>0.7463395485979035</v>
+        <v>0.395008093189036</v>
       </c>
       <c r="G63">
-        <v>1.626861105477901</v>
+        <v>1.765617021486599</v>
       </c>
       <c r="H63">
-        <v>-0.55073853999547</v>
+        <v>-0.5413329118150904</v>
       </c>
       <c r="I63">
-        <v>0.8608196858713737</v>
+        <v>1.006167846576003</v>
       </c>
       <c r="J63">
-        <v>-0.6541849312033112</v>
+        <v>-0.4492926666340341</v>
       </c>
       <c r="K63">
         <v>4.334853618087458</v>
@@ -13411,19 +13411,19 @@
         <v>0.1277499607810824</v>
       </c>
       <c r="AD63">
-        <v>2.202842379388367</v>
+        <v>3.33128034957527</v>
       </c>
       <c r="AE63">
-        <v>0.8876171964688915</v>
+        <v>0.7701350771204978</v>
       </c>
       <c r="AF63">
-        <v>1.344948426046934</v>
+        <v>1.259028496010243</v>
       </c>
       <c r="AG63">
-        <v>0.2751986501962092</v>
+        <v>0.2224800822943524</v>
       </c>
       <c r="AH63">
-        <v>0.1658703626138485</v>
+        <v>0.3121529441863116</v>
       </c>
       <c r="AI63">
         <v>-1.166311921148972</v>
@@ -13546,19 +13546,19 @@
         <v>-0.295583451147202</v>
       </c>
       <c r="F64">
-        <v>2.3030740173315</v>
+        <v>2.228187044307289</v>
       </c>
       <c r="G64">
-        <v>-0.2556826737404539</v>
+        <v>0.1562163997922407</v>
       </c>
       <c r="H64">
-        <v>-1.361806228739506</v>
+        <v>-1.142389581005778</v>
       </c>
       <c r="I64">
-        <v>1.420678587076384</v>
+        <v>1.517020003087572</v>
       </c>
       <c r="J64">
-        <v>-0.04529262503531556</v>
+        <v>-0.0305820767084502</v>
       </c>
       <c r="K64">
         <v>5.562527967999203</v>
@@ -13618,19 +13618,19 @@
         <v>0.4545797288102055</v>
       </c>
       <c r="AD64">
-        <v>1.759209575634501</v>
+        <v>1.6768353549473</v>
       </c>
       <c r="AE64">
-        <v>-2.845187308611023</v>
+        <v>-3.02277330201168</v>
       </c>
       <c r="AF64">
-        <v>-0.3107356506646884</v>
+        <v>-0.2114467077378147</v>
       </c>
       <c r="AG64">
-        <v>-0.5422636470894634</v>
+        <v>-0.1521259166330003</v>
       </c>
       <c r="AH64">
-        <v>-0.2170169044746975</v>
+        <v>-0.5869920303535531</v>
       </c>
       <c r="AI64">
         <v>0.04578202963086297</v>
@@ -13753,19 +13753,19 @@
         <v>-0.06022291976584404</v>
       </c>
       <c r="F65">
-        <v>3.648631560487245</v>
+        <v>3.874428594990037</v>
       </c>
       <c r="G65">
-        <v>-2.151484794923416</v>
+        <v>-1.496042797719765</v>
       </c>
       <c r="H65">
-        <v>-1.351450743369681</v>
+        <v>-0.9691337358978636</v>
       </c>
       <c r="I65">
-        <v>0.5361857415251998</v>
+        <v>0.5104556329389274</v>
       </c>
       <c r="J65">
-        <v>1.194383183648506</v>
+        <v>0.517141371180313</v>
       </c>
       <c r="K65">
         <v>3.210560005653205</v>
@@ -13825,19 +13825,19 @@
         <v>0.07771325037466009</v>
       </c>
       <c r="AD65">
-        <v>1.595262718814727</v>
+        <v>1.739902440556698</v>
       </c>
       <c r="AE65">
-        <v>-1.935197961946008</v>
+        <v>-2.07678079891269</v>
       </c>
       <c r="AF65">
-        <v>0.1413899944144496</v>
+        <v>0.203961471677659</v>
       </c>
       <c r="AG65">
-        <v>-0.1554323374534092</v>
+        <v>-0.1166891462799627</v>
       </c>
       <c r="AH65">
-        <v>0.1670316893798421</v>
+        <v>-0.1891885564883333</v>
       </c>
       <c r="AI65">
         <v>-0.5581566447401478</v>
@@ -13960,19 +13960,19 @@
         <v>0.1474233616151251</v>
       </c>
       <c r="F66">
-        <v>0.2227367028970157</v>
+        <v>0.1406197219736557</v>
       </c>
       <c r="G66">
-        <v>-0.5367882022765263</v>
+        <v>-0.3623607109804633</v>
       </c>
       <c r="H66">
-        <v>1.194001773565668</v>
+        <v>1.306677326371274</v>
       </c>
       <c r="I66">
-        <v>1.251404453317703</v>
+        <v>1.427050432567783</v>
       </c>
       <c r="J66">
-        <v>-1.047519684673522</v>
+        <v>-0.5829317243042438</v>
       </c>
       <c r="K66">
         <v>-2.946249378928491</v>
@@ -14032,19 +14032,19 @@
         <v>0.2013088617138568</v>
       </c>
       <c r="AD66">
-        <v>-0.7292875711071578</v>
+        <v>-0.6592187700434945</v>
       </c>
       <c r="AE66">
-        <v>-0.2077548646391924</v>
+        <v>-0.07745993636694007</v>
       </c>
       <c r="AF66">
-        <v>0.1626980001314655</v>
+        <v>0.3083851054358426</v>
       </c>
       <c r="AG66">
-        <v>0.4669510679911414</v>
+        <v>-0.7636148787943876</v>
       </c>
       <c r="AH66">
-        <v>0.07191530282060071</v>
+        <v>0.3042389760936004</v>
       </c>
       <c r="AI66">
         <v>1.206002748003832</v>
@@ -14167,19 +14167,19 @@
         <v>-0.3858243308135781</v>
       </c>
       <c r="F67">
-        <v>1.382813390309055</v>
+        <v>1.151558410305823</v>
       </c>
       <c r="G67">
-        <v>0.953001138614221</v>
+        <v>1.17493725088693</v>
       </c>
       <c r="H67">
-        <v>-0.8845832928987344</v>
+        <v>-0.8554699313803148</v>
       </c>
       <c r="I67">
-        <v>-0.7281907492501161</v>
+        <v>-0.8627027270465959</v>
       </c>
       <c r="J67">
-        <v>1.026969558179885</v>
+        <v>0.5599753231761587</v>
       </c>
       <c r="K67">
         <v>1.589371061447239</v>
@@ -14239,19 +14239,19 @@
         <v>0.0613683240638713</v>
       </c>
       <c r="AD67">
-        <v>0.04356307965473912</v>
+        <v>-0.2813197344280739</v>
       </c>
       <c r="AE67">
-        <v>-0.6691106990402781</v>
+        <v>-0.7225233217602479</v>
       </c>
       <c r="AF67">
-        <v>-0.3784672937987154</v>
+        <v>-0.3964594465280145</v>
       </c>
       <c r="AG67">
-        <v>-0.1147696177676812</v>
+        <v>0.08748957253412359</v>
       </c>
       <c r="AH67">
-        <v>0.07348601038419326</v>
+        <v>-0.09265386208770934</v>
       </c>
       <c r="AI67">
         <v>0.1625831628361291</v>
@@ -14374,19 +14374,19 @@
         <v>-0.3434620704963828</v>
       </c>
       <c r="F68">
-        <v>0.2145500172818351</v>
+        <v>-0.08544271061321142</v>
       </c>
       <c r="G68">
-        <v>1.744822665321943</v>
+        <v>1.738071268634809</v>
       </c>
       <c r="H68">
-        <v>-1.15913452176891</v>
+        <v>-1.213506560550673</v>
       </c>
       <c r="I68">
-        <v>-0.2160950225858022</v>
+        <v>-0.1044163071741808</v>
       </c>
       <c r="J68">
-        <v>-0.476974814787925</v>
+        <v>-0.4716903561160415</v>
       </c>
       <c r="K68">
         <v>1.557899393027626</v>
@@ -14446,19 +14446,19 @@
         <v>-0.17903367405288</v>
       </c>
       <c r="AD68">
-        <v>1.08724854641561</v>
+        <v>1.797816712719591</v>
       </c>
       <c r="AE68">
-        <v>0.5461601356566703</v>
+        <v>0.4952792050960885</v>
       </c>
       <c r="AF68">
-        <v>0.6247547780878249</v>
+        <v>0.6248180929437895</v>
       </c>
       <c r="AG68">
-        <v>-0.2933381070308989</v>
+        <v>-0.1036895493891711</v>
       </c>
       <c r="AH68">
-        <v>0.03779721255926703</v>
+        <v>-0.343588326481639</v>
       </c>
       <c r="AI68">
         <v>0.1962487977882144</v>
@@ -14581,19 +14581,19 @@
         <v>-0.01975570701402771</v>
       </c>
       <c r="F69">
-        <v>0.9613107032587818</v>
+        <v>0.8386599953334356</v>
       </c>
       <c r="G69">
-        <v>-0.265345063049673</v>
+        <v>-0.008101613439714226</v>
       </c>
       <c r="H69">
-        <v>-0.2266705093455169</v>
+        <v>-0.05867129537596474</v>
       </c>
       <c r="I69">
-        <v>0.7176542644476077</v>
+        <v>0.8727981201319327</v>
       </c>
       <c r="J69">
-        <v>-0.3147631266349329</v>
+        <v>-0.401526238347536</v>
       </c>
       <c r="K69">
         <v>-1.675073112988197</v>
@@ -14653,19 +14653,19 @@
         <v>-0.5431520301716892</v>
       </c>
       <c r="AD69">
-        <v>0.6144391139813635</v>
+        <v>0.7894314868418174</v>
       </c>
       <c r="AE69">
-        <v>0.3782082479440951</v>
+        <v>0.3089131497729245</v>
       </c>
       <c r="AF69">
-        <v>-0.5738973291858682</v>
+        <v>-0.6038764129602521</v>
       </c>
       <c r="AG69">
-        <v>-0.2043918831644752</v>
+        <v>0.1416366893578303</v>
       </c>
       <c r="AH69">
-        <v>-0.181054265499349</v>
+        <v>-0.1636618552684567</v>
       </c>
       <c r="AI69">
         <v>0.1678372183253347</v>
@@ -14788,19 +14788,19 @@
         <v>-0.101870243462264</v>
       </c>
       <c r="F70">
-        <v>1.95690206457493</v>
+        <v>1.877832115071721</v>
       </c>
       <c r="G70">
-        <v>-0.4853307818422667</v>
+        <v>-0.08528558409473926</v>
       </c>
       <c r="H70">
-        <v>-0.4377998834409981</v>
+        <v>-0.2445337447041225</v>
       </c>
       <c r="I70">
-        <v>-0.6686977263366144</v>
+        <v>-0.6677719503860663</v>
       </c>
       <c r="J70">
-        <v>0.7939297700689303</v>
+        <v>0.1220346688837808</v>
       </c>
       <c r="K70">
         <v>3.575522183381201</v>
@@ -14860,19 +14860,19 @@
         <v>-0.2033188400797162</v>
       </c>
       <c r="AD70">
-        <v>0.3453559457380456</v>
+        <v>-0.07012478193376488</v>
       </c>
       <c r="AE70">
-        <v>-2.22858012340127</v>
+        <v>-2.298918175964697</v>
       </c>
       <c r="AF70">
-        <v>-0.5276822957328621</v>
+        <v>-0.4156126006010016</v>
       </c>
       <c r="AG70">
-        <v>-0.05298305873714337</v>
+        <v>-0.3346400429442152</v>
       </c>
       <c r="AH70">
-        <v>0.05958518891851777</v>
+        <v>-0.126891609994511</v>
       </c>
       <c r="AI70">
         <v>-0.600472548413696</v>
@@ -14995,19 +14995,19 @@
         <v>0.24634192796449</v>
       </c>
       <c r="F71">
-        <v>-0.1965655957400324</v>
+        <v>-0.5394740855988055</v>
       </c>
       <c r="G71">
-        <v>1.913398319609906</v>
+        <v>1.869812644096615</v>
       </c>
       <c r="H71">
-        <v>-0.1107084441104491</v>
+        <v>-0.2164032115724876</v>
       </c>
       <c r="I71">
-        <v>0.4033498225254863</v>
+        <v>0.4285982003899671</v>
       </c>
       <c r="J71">
-        <v>-0.3787390113056249</v>
+        <v>-0.1145053786519487</v>
       </c>
       <c r="K71">
         <v>1.640638725174716</v>
@@ -15067,19 +15067,19 @@
         <v>0.1454456379287856</v>
       </c>
       <c r="AD71">
-        <v>2.688237180906775</v>
+        <v>3.832579803298468</v>
       </c>
       <c r="AE71">
-        <v>2.125187242214348</v>
+        <v>1.841404467527931</v>
       </c>
       <c r="AF71">
-        <v>-0.9255074778411998</v>
+        <v>-1.065242027089778</v>
       </c>
       <c r="AG71">
-        <v>0.1174027813020833</v>
+        <v>-0.212158204966075</v>
       </c>
       <c r="AH71">
-        <v>-0.2999435860954894</v>
+        <v>0.07299655266021839</v>
       </c>
       <c r="AI71">
         <v>-1.450818341256115</v>
@@ -15202,19 +15202,19 @@
         <v>0.01821023129272615</v>
       </c>
       <c r="F72">
-        <v>-4.356356562663269</v>
+        <v>-4.539485101351825</v>
       </c>
       <c r="G72">
-        <v>2.428582058475992</v>
+        <v>1.57029385026753</v>
       </c>
       <c r="H72">
-        <v>0.1613401718198585</v>
+        <v>-0.3137175049773528</v>
       </c>
       <c r="I72">
-        <v>3.599612891481097</v>
+        <v>2.98757476048945</v>
       </c>
       <c r="J72">
-        <v>1.27018238632008</v>
+        <v>2.619950661345187</v>
       </c>
       <c r="K72">
         <v>-10.68945466831982</v>
@@ -15274,19 +15274,19 @@
         <v>0.6986316699376069</v>
       </c>
       <c r="AD72">
-        <v>-5.227532921612816</v>
+        <v>-6.766339137628891</v>
       </c>
       <c r="AE72">
-        <v>-0.5471902821591643</v>
+        <v>-0.02035958398906756</v>
       </c>
       <c r="AF72">
-        <v>0.5773928344982386</v>
+        <v>0.7453913033735662</v>
       </c>
       <c r="AG72">
-        <v>-0.01775999974000012</v>
+        <v>0.3935071126696424</v>
       </c>
       <c r="AH72">
-        <v>0.1409576522975354</v>
+        <v>0.07949952978907404</v>
       </c>
       <c r="AI72">
         <v>0.04221854727543864</v>
@@ -15409,19 +15409,19 @@
         <v>0.1408287905251675</v>
       </c>
       <c r="F73">
-        <v>-7.718604383815078</v>
+        <v>-6.669619183695862</v>
       </c>
       <c r="G73">
-        <v>-4.93060120230859</v>
+        <v>-6.253669099100267</v>
       </c>
       <c r="H73">
-        <v>-1.016625969171751</v>
+        <v>-1.172479535910638</v>
       </c>
       <c r="I73">
-        <v>2.666588589676996</v>
+        <v>1.918228403393246</v>
       </c>
       <c r="J73">
-        <v>2.858118090083305</v>
+        <v>3.31724142743409</v>
       </c>
       <c r="K73">
         <v>-3.320111047482329</v>
@@ -15481,19 +15481,19 @@
         <v>0.2111120879392076</v>
       </c>
       <c r="AD73">
-        <v>-3.446971864774098</v>
+        <v>-4.498974900937135</v>
       </c>
       <c r="AE73">
-        <v>0.1071821900418558</v>
+        <v>0.4053003459978668</v>
       </c>
       <c r="AF73">
-        <v>-0.3747465053142328</v>
+        <v>-0.2795473691588286</v>
       </c>
       <c r="AG73">
-        <v>-0.06663490647596096</v>
+        <v>-0.1602694221286596</v>
       </c>
       <c r="AH73">
-        <v>-0.05953707240452505</v>
+        <v>-0.09695712046082036</v>
       </c>
       <c r="AI73">
         <v>-1.223322755949776</v>
@@ -15616,19 +15616,19 @@
         <v>0.1415615206462738</v>
       </c>
       <c r="F74">
-        <v>0.2072833177488491</v>
+        <v>-0.1143772772347529</v>
       </c>
       <c r="G74">
-        <v>1.232672720856785</v>
+        <v>1.3536324101197</v>
       </c>
       <c r="H74">
-        <v>2.146507618261829</v>
+        <v>2.047539115704761</v>
       </c>
       <c r="I74">
-        <v>0.8027032954385083</v>
+        <v>0.6520741141914576</v>
       </c>
       <c r="J74">
-        <v>-0.07972162760208107</v>
+        <v>0.521948391965094</v>
       </c>
       <c r="K74">
         <v>-4.130523486125573</v>
@@ -15688,19 +15688,19 @@
         <v>0.3116022086569717</v>
       </c>
       <c r="AD74">
-        <v>-0.03527131789163493</v>
+        <v>0.50927684159165</v>
       </c>
       <c r="AE74">
-        <v>1.279619271679357</v>
+        <v>1.364781525648434</v>
       </c>
       <c r="AF74">
-        <v>0.8688799389734392</v>
+        <v>0.8486383287527222</v>
       </c>
       <c r="AG74">
-        <v>-0.06483510577867097</v>
+        <v>0.3834573343962174</v>
       </c>
       <c r="AH74">
-        <v>0.2721232495994222</v>
+        <v>0.01535099374310323</v>
       </c>
       <c r="AI74">
         <v>-1.235173817549428</v>
@@ -15823,19 +15823,19 @@
         <v>0.1672070748849981</v>
       </c>
       <c r="F75">
-        <v>-2.916727768455741</v>
+        <v>-2.387471419172927</v>
       </c>
       <c r="G75">
-        <v>-3.116414089795814</v>
+        <v>-3.578308691474241</v>
       </c>
       <c r="H75">
-        <v>-2.421847999220778</v>
+        <v>-2.244465012596514</v>
       </c>
       <c r="I75">
-        <v>-0.1977854321418537</v>
+        <v>0.1656406671610217</v>
       </c>
       <c r="J75">
-        <v>-1.100485963410287</v>
+        <v>-1.333760041315664</v>
       </c>
       <c r="K75">
         <v>-3.936206664357037</v>
@@ -15895,19 +15895,19 @@
         <v>0.3205813722190608</v>
       </c>
       <c r="AD75">
-        <v>-2.937297814258928</v>
+        <v>-3.734671653388264</v>
       </c>
       <c r="AE75">
-        <v>0.1298203070172723</v>
+        <v>0.3986474964453412</v>
       </c>
       <c r="AF75">
-        <v>0.0008291385178073041</v>
+        <v>0.08661802030142374</v>
       </c>
       <c r="AG75">
-        <v>-0.4879679419176874</v>
+        <v>-0.07158348492934068</v>
       </c>
       <c r="AH75">
-        <v>0.009972493835075784</v>
+        <v>-0.5183841458517591</v>
       </c>
       <c r="AI75">
         <v>3.605465289960756</v>
@@ -16030,19 +16030,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F76">
-        <v>-3.499167012772824</v>
+        <v>-3.214982390104044</v>
       </c>
       <c r="G76">
-        <v>-1.251590681657597</v>
+        <v>-1.849852170349287</v>
       </c>
       <c r="H76">
-        <v>-0.7015830678172399</v>
+        <v>-0.8007248845781875</v>
       </c>
       <c r="I76">
-        <v>0.6974117447357491</v>
+        <v>0.483770267667513</v>
       </c>
       <c r="J76">
-        <v>0.778011394278378</v>
+        <v>0.9263921850672217</v>
       </c>
       <c r="K76">
         <v>-7.498793515849654</v>
@@ -16102,19 +16102,19 @@
         <v>1.029256423159631</v>
       </c>
       <c r="AD76">
-        <v>-3.052506720634756</v>
+        <v>-3.816373613732942</v>
       </c>
       <c r="AE76">
-        <v>0.5443465657415898</v>
+        <v>0.8241743609739222</v>
       </c>
       <c r="AF76">
-        <v>-0.01452368116795111</v>
+        <v>0.05321451782250264</v>
       </c>
       <c r="AG76">
-        <v>-0.4694637037023855</v>
+        <v>-0.1789717711150476</v>
       </c>
       <c r="AH76">
-        <v>-0.26170763988898</v>
+        <v>-0.5258786967681923</v>
       </c>
       <c r="AI76">
         <v>0.8085651337891449</v>
@@ -16237,19 +16237,19 @@
         <v>0.1356996796774226</v>
       </c>
       <c r="F77">
-        <v>0.1624392106286633</v>
+        <v>-0.1700175630621883</v>
       </c>
       <c r="G77">
-        <v>1.768262722603912</v>
+        <v>1.787634053043936</v>
       </c>
       <c r="H77">
-        <v>-0.1977504257907908</v>
+        <v>-0.2790061412889446</v>
       </c>
       <c r="I77">
-        <v>-0.04603822410625486</v>
+        <v>-0.07578349483703979</v>
       </c>
       <c r="J77">
-        <v>0.106505071654752</v>
+        <v>0.102539946772146</v>
       </c>
       <c r="K77">
         <v>2.350334193974971</v>
@@ -16309,19 +16309,19 @@
         <v>0.2880340327103311</v>
       </c>
       <c r="AD77">
-        <v>1.108501687481541</v>
+        <v>2.142340290080005</v>
       </c>
       <c r="AE77">
-        <v>0.3770890886399601</v>
+        <v>0.4179690594966713</v>
       </c>
       <c r="AF77">
-        <v>1.418899150667578</v>
+        <v>1.509271052902518</v>
       </c>
       <c r="AG77">
-        <v>0.4841212422155218</v>
+        <v>-0.2133969840553999</v>
       </c>
       <c r="AH77">
-        <v>-0.1513394496109454</v>
+        <v>0.4217855838897661</v>
       </c>
       <c r="AI77">
         <v>0.358089551576086</v>
@@ -16444,19 +16444,19 @@
         <v>-0.02320148452344964</v>
       </c>
       <c r="F78">
-        <v>0.82179842508351</v>
+        <v>0.7040131653336236</v>
       </c>
       <c r="G78">
-        <v>0.07097086043683611</v>
+        <v>0.2427494036110708</v>
       </c>
       <c r="H78">
-        <v>-1.201733111767312</v>
+        <v>-1.07230816120923</v>
       </c>
       <c r="I78">
-        <v>-0.2382401567685146</v>
+        <v>-0.1294980555615288</v>
       </c>
       <c r="J78">
-        <v>0.161503491698493</v>
+        <v>-0.2876461713571243</v>
       </c>
       <c r="K78">
         <v>2.89571496565968</v>
@@ -16516,19 +16516,19 @@
         <v>-0.1768989418720761</v>
       </c>
       <c r="AD78">
-        <v>1.242775121577969</v>
+        <v>1.86658633345099</v>
       </c>
       <c r="AE78">
-        <v>0.1950714531278918</v>
+        <v>0.0732512318860665</v>
       </c>
       <c r="AF78">
-        <v>-0.310765676987514</v>
+        <v>-0.2473550910079182</v>
       </c>
       <c r="AG78">
-        <v>-0.03553902757623593</v>
+        <v>-0.971566813887056</v>
       </c>
       <c r="AH78">
-        <v>-0.01909347709499865</v>
+        <v>-0.2790951098509891</v>
       </c>
       <c r="AI78">
         <v>-0.8123421154952789</v>
@@ -16651,19 +16651,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F79">
-        <v>-0.4920766053336235</v>
+        <v>-0.7390705507972136</v>
       </c>
       <c r="G79">
-        <v>1.267012245098334</v>
+        <v>1.202258609539834</v>
       </c>
       <c r="H79">
-        <v>0.7978347222553993</v>
+        <v>0.6657391973987322</v>
       </c>
       <c r="I79">
-        <v>-1.699906320845899</v>
+        <v>-1.819255901013059</v>
       </c>
       <c r="J79">
-        <v>0.5539457833098396</v>
+        <v>0.2060529573694063</v>
       </c>
       <c r="K79">
         <v>-2.222816435941934</v>
@@ -16723,19 +16723,19 @@
         <v>0.3039710741465705</v>
       </c>
       <c r="AD79">
-        <v>-1.416550687829511</v>
+        <v>-1.309871802973513</v>
       </c>
       <c r="AE79">
-        <v>0.3385961964274331</v>
+        <v>0.559114304575326</v>
       </c>
       <c r="AF79">
-        <v>1.270638965798116</v>
+        <v>1.380931736570131</v>
       </c>
       <c r="AG79">
-        <v>0.3509097561064929</v>
+        <v>-0.4785845834524489</v>
       </c>
       <c r="AH79">
-        <v>0.01595144111893106</v>
+        <v>0.2211024969336655</v>
       </c>
       <c r="AI79">
         <v>-1.159792376240714</v>
@@ -16858,19 +16858,19 @@
         <v>0.1444924411306995</v>
       </c>
       <c r="F80">
-        <v>-0.1596586245528225</v>
+        <v>-0.4936177809295538</v>
       </c>
       <c r="G80">
-        <v>1.509501863756175</v>
+        <v>1.534992022946944</v>
       </c>
       <c r="H80">
-        <v>0.9795820324581831</v>
+        <v>0.8984805140841058</v>
       </c>
       <c r="I80">
-        <v>0.06089269727427633</v>
+        <v>0.09192285940695311</v>
       </c>
       <c r="J80">
-        <v>-0.3627729962812405</v>
+        <v>-0.1910173451008331</v>
       </c>
       <c r="K80">
         <v>1.483933812146157</v>
@@ -16930,19 +16930,19 @@
         <v>-1.184041179670209</v>
       </c>
       <c r="AD80">
-        <v>0.7624558082034327</v>
+        <v>1.209931332471371</v>
       </c>
       <c r="AE80">
-        <v>1.470713276902939</v>
+        <v>1.412431867249178</v>
       </c>
       <c r="AF80">
-        <v>0.2616757961947982</v>
+        <v>0.1253356883033094</v>
       </c>
       <c r="AG80">
-        <v>0.4809520470140139</v>
+        <v>0.4281537858276629</v>
       </c>
       <c r="AH80">
-        <v>0.049995817835377</v>
+        <v>0.5948223539867695</v>
       </c>
       <c r="AI80">
         <v>1.300397791599026</v>
@@ -17065,19 +17065,19 @@
         <v>0.1393633302829546</v>
       </c>
       <c r="F81">
-        <v>-0.01622939440955766</v>
+        <v>0.3823055552684769</v>
       </c>
       <c r="G81">
-        <v>0.8898184822216836</v>
+        <v>0.519778386992981</v>
       </c>
       <c r="H81">
-        <v>-1.127942858233192</v>
+        <v>-1.43383840817679</v>
       </c>
       <c r="I81">
-        <v>1.103258510701185</v>
+        <v>0.8698373225258111</v>
       </c>
       <c r="J81">
-        <v>-0.06065555302388964</v>
+        <v>0.8113123968820116</v>
       </c>
       <c r="K81">
         <v>-2.455481236815557</v>
@@ -17137,19 +17137,19 @@
         <v>-0.9863089460686889</v>
       </c>
       <c r="AD81">
-        <v>-0.0812147330627592</v>
+        <v>-0.4166040730021636</v>
       </c>
       <c r="AE81">
-        <v>-0.3357036029187511</v>
+        <v>-0.3976214767082862</v>
       </c>
       <c r="AF81">
-        <v>-0.7557560341849772</v>
+        <v>-0.7777504686872583</v>
       </c>
       <c r="AG81">
-        <v>-0.499436975447984</v>
+        <v>-0.115125941697036</v>
       </c>
       <c r="AH81">
-        <v>-0.01451328569206958</v>
+        <v>-0.5316121970468248</v>
       </c>
       <c r="AI81">
         <v>1.470363794322064</v>
@@ -17272,19 +17272,19 @@
         <v>-0.04788465051463128</v>
       </c>
       <c r="F82">
-        <v>0.7486001298139825</v>
+        <v>0.654008331612851</v>
       </c>
       <c r="G82">
-        <v>-0.6537560069908108</v>
+        <v>-0.383873029427946</v>
       </c>
       <c r="H82">
-        <v>0.6514011077199057</v>
+        <v>0.8316894010995539</v>
       </c>
       <c r="I82">
-        <v>-0.1102690668159531</v>
+        <v>0.1562131120490419</v>
       </c>
       <c r="J82">
-        <v>-0.8512755903325802</v>
+        <v>-0.9999036648676071</v>
       </c>
       <c r="K82">
         <v>-0.4716995353729246</v>
@@ -17344,19 +17344,19 @@
         <v>-0.1634747792428063</v>
       </c>
       <c r="AD82">
-        <v>0.1375175205617371</v>
+        <v>0.3050562611022868</v>
       </c>
       <c r="AE82">
-        <v>0.8938989174241313</v>
+        <v>0.8770817020750971</v>
       </c>
       <c r="AF82">
-        <v>-0.2902010091470309</v>
+        <v>-0.3350968630709499</v>
       </c>
       <c r="AG82">
-        <v>0.5231245220012147</v>
+        <v>0.2202174936495753</v>
       </c>
       <c r="AH82">
-        <v>-0.01799411548352827</v>
+        <v>0.5951356537990585</v>
       </c>
       <c r="AI82">
         <v>0.2356831719981778</v>
@@ -17479,19 +17479,19 @@
         <v>-0.1129168127280604</v>
       </c>
       <c r="F83">
-        <v>-0.1742547707542405</v>
+        <v>0.0347488878144709</v>
       </c>
       <c r="G83">
-        <v>-2.548192601395607</v>
+        <v>-2.392362945187375</v>
       </c>
       <c r="H83">
-        <v>0.6490544614373318</v>
+        <v>0.9073585075807635</v>
       </c>
       <c r="I83">
-        <v>-0.4870216820625809</v>
+        <v>-0.2565848727740626</v>
       </c>
       <c r="J83">
-        <v>-0.4565597018797958</v>
+        <v>-0.845378392538665</v>
       </c>
       <c r="K83">
         <v>-0.3361813078198692</v>
@@ -17551,19 +17551,19 @@
         <v>0.2191746359274922</v>
       </c>
       <c r="AD83">
-        <v>-1.387751362197188</v>
+        <v>-2.047988863987779</v>
       </c>
       <c r="AE83">
-        <v>-0.7134665702219555</v>
+        <v>-0.6150955762947308</v>
       </c>
       <c r="AF83">
-        <v>-0.736049590353747</v>
+        <v>-0.6455932395054421</v>
       </c>
       <c r="AG83">
-        <v>0.6247192754445139</v>
+        <v>-0.1373767199298988</v>
       </c>
       <c r="AH83">
-        <v>-0.06280651749336262</v>
+        <v>0.6248910153967007</v>
       </c>
       <c r="AI83">
         <v>1.72568518470413</v>
@@ -17686,19 +17686,19 @@
         <v>-0.06105854231240382</v>
       </c>
       <c r="F84">
-        <v>-2.043375171374394</v>
+        <v>-1.915493883872965</v>
       </c>
       <c r="G84">
-        <v>-0.3853545853382637</v>
+        <v>-0.7779118368411341</v>
       </c>
       <c r="H84">
-        <v>-1.640250870256684</v>
+        <v>-1.702685602910563</v>
       </c>
       <c r="I84">
-        <v>-1.299450108370559</v>
+        <v>-1.438312371007366</v>
       </c>
       <c r="J84">
-        <v>1.115429624346499</v>
+        <v>0.4975544732086226</v>
       </c>
       <c r="K84">
         <v>2.879647543773961</v>
@@ -17758,19 +17758,19 @@
         <v>-1.397599887148663</v>
       </c>
       <c r="AD84">
-        <v>-2.383875601153178</v>
+        <v>-3.403714422070412</v>
       </c>
       <c r="AE84">
-        <v>-0.5224938374408571</v>
+        <v>-0.3729575437517335</v>
       </c>
       <c r="AF84">
-        <v>-0.7341601495210128</v>
+        <v>-0.6700215715932984</v>
       </c>
       <c r="AG84">
-        <v>-0.2610588568449501</v>
+        <v>-0.2283740370151802</v>
       </c>
       <c r="AH84">
-        <v>0.01167181307679237</v>
+        <v>-0.3143787487361859</v>
       </c>
       <c r="AI84">
         <v>1.189976391279918</v>
@@ -17893,19 +17893,19 @@
         <v>-0.1911767692042713</v>
       </c>
       <c r="F85">
-        <v>2.701819707689727</v>
+        <v>2.660100915954967</v>
       </c>
       <c r="G85">
-        <v>-1.019122523316895</v>
+        <v>-0.4843935734939727</v>
       </c>
       <c r="H85">
-        <v>-1.726731464038807</v>
+        <v>-1.38802272523879</v>
       </c>
       <c r="I85">
-        <v>0.4236668887060378</v>
+        <v>0.5356698778241705</v>
       </c>
       <c r="J85">
-        <v>0.5694821790352862</v>
+        <v>-0.05961257406078871</v>
       </c>
       <c r="K85">
         <v>6.276050423349169</v>
@@ -17965,19 +17965,19 @@
         <v>0.4704266568185702</v>
       </c>
       <c r="AD85">
-        <v>2.377786510668908</v>
+        <v>2.516835379533499</v>
       </c>
       <c r="AE85">
-        <v>-3.220759171631432</v>
+        <v>-3.401872200349805</v>
       </c>
       <c r="AF85">
-        <v>0.5261959735818638</v>
+        <v>0.6177036410247642</v>
       </c>
       <c r="AG85">
-        <v>0.4422573321711865</v>
+        <v>0.154403883520091</v>
       </c>
       <c r="AH85">
-        <v>-0.002761465039437614</v>
+        <v>0.4904309474575311</v>
       </c>
       <c r="AI85">
         <v>-1.212417599873017</v>
@@ -18100,19 +18100,19 @@
         <v>-0.2647910308989401</v>
       </c>
       <c r="F86">
-        <v>2.660840234718088</v>
+        <v>3.927636512457186</v>
       </c>
       <c r="G86">
-        <v>-2.085374815893958</v>
+        <v>-2.194968087799314</v>
       </c>
       <c r="H86">
-        <v>0.3152280308312177</v>
+        <v>0.04864602490335349</v>
       </c>
       <c r="I86">
-        <v>0.349028667563612</v>
+        <v>-0.119787346410673</v>
       </c>
       <c r="J86">
-        <v>0.7457955201523205</v>
+        <v>1.565063596388053</v>
       </c>
       <c r="K86">
         <v>4.787954224406309</v>
@@ -18172,19 +18172,19 @@
         <v>0.02845396200163319</v>
       </c>
       <c r="AD86">
-        <v>1.422178612744733</v>
+        <v>1.606996291175687</v>
       </c>
       <c r="AE86">
-        <v>-1.955612062925864</v>
+        <v>-2.041811234155997</v>
       </c>
       <c r="AF86">
-        <v>0.7798006318391821</v>
+        <v>0.8395422979071555</v>
       </c>
       <c r="AG86">
-        <v>-0.09801048215780624</v>
+        <v>0.1337199870996474</v>
       </c>
       <c r="AH86">
-        <v>0.08247765960815193</v>
+        <v>-0.07848054926005915</v>
       </c>
       <c r="AI86">
         <v>-1.429776533246839</v>
@@ -18307,19 +18307,19 @@
         <v>0.1408287905251675</v>
       </c>
       <c r="F87">
-        <v>-0.5876809192514295</v>
+        <v>-0.8073903800899545</v>
       </c>
       <c r="G87">
-        <v>1.323212867680873</v>
+        <v>1.201241625711369</v>
       </c>
       <c r="H87">
-        <v>-0.5091884924767798</v>
+        <v>-0.6008362430517398</v>
       </c>
       <c r="I87">
-        <v>-0.04607227438443697</v>
+        <v>-0.007622349256917529</v>
       </c>
       <c r="J87">
-        <v>-0.3631573908886393</v>
+        <v>-0.212509032369674</v>
       </c>
       <c r="K87">
         <v>-1.639293074578072</v>
@@ -18379,19 +18379,19 @@
         <v>0.1332702464437879</v>
       </c>
       <c r="AD87">
-        <v>-1.587586146498063</v>
+        <v>-1.636347781195395</v>
       </c>
       <c r="AE87">
-        <v>0.529108731029116</v>
+        <v>0.765533675883608</v>
       </c>
       <c r="AF87">
-        <v>0.9385879067366193</v>
+        <v>0.9996513996118386</v>
       </c>
       <c r="AG87">
-        <v>-0.299936951989778</v>
+        <v>0.3256735252218673</v>
       </c>
       <c r="AH87">
-        <v>0.008001402621872617</v>
+        <v>-0.2375345388536221</v>
       </c>
       <c r="AI87">
         <v>-1.307420061342078</v>
@@ -18514,19 +18514,19 @@
         <v>-0.1414336413925353</v>
       </c>
       <c r="F88">
-        <v>3.710607312888591</v>
+        <v>4.947571595924446</v>
       </c>
       <c r="G88">
-        <v>-0.7246762243819574</v>
+        <v>-0.8519398701271076</v>
       </c>
       <c r="H88">
-        <v>-1.613156874095792</v>
+        <v>-1.98826006654541</v>
       </c>
       <c r="I88">
-        <v>-0.4582232954369789</v>
+        <v>-1.105452409190314</v>
       </c>
       <c r="J88">
-        <v>1.717179578505471</v>
+        <v>2.217494397253776</v>
       </c>
       <c r="K88">
         <v>6.703200406785616</v>
@@ -18586,19 +18586,19 @@
         <v>0.2106627874167905</v>
       </c>
       <c r="AD88">
-        <v>2.298660002864017</v>
+        <v>1.698570390145999</v>
       </c>
       <c r="AE88">
-        <v>-3.65017534635435</v>
+        <v>-3.935235845384958</v>
       </c>
       <c r="AF88">
-        <v>0.311493383302043</v>
+        <v>0.2055661791825183</v>
       </c>
       <c r="AG88">
-        <v>-0.05768556013755081</v>
+        <v>0.9256574557544647</v>
       </c>
       <c r="AH88">
-        <v>0.07681335261915993</v>
+        <v>0.163045537380811</v>
       </c>
       <c r="AI88">
         <v>0.3335727604480915</v>
@@ -18721,19 +18721,19 @@
         <v>0.2619694063724631</v>
       </c>
       <c r="F89">
-        <v>-0.8351006702161037</v>
+        <v>-1.039417063827579</v>
       </c>
       <c r="G89">
-        <v>0.3549382089009669</v>
+        <v>0.3563020563274675</v>
       </c>
       <c r="H89">
-        <v>2.25290098589854</v>
+        <v>2.218935816606601</v>
       </c>
       <c r="I89">
-        <v>-1.298435217708467</v>
+        <v>-1.126598258796411</v>
       </c>
       <c r="J89">
-        <v>-0.8368865780758705</v>
+        <v>-0.9456257003949767</v>
       </c>
       <c r="K89">
         <v>2.840511015231958</v>
@@ -18793,19 +18793,19 @@
         <v>-1.078159308486627</v>
       </c>
       <c r="AD89">
-        <v>0.2426018985200276</v>
+        <v>0.5281216381836815</v>
       </c>
       <c r="AE89">
-        <v>1.156580996106513</v>
+        <v>1.177277553273649</v>
       </c>
       <c r="AF89">
-        <v>0.03966529121407797</v>
+        <v>-0.0406232484497967</v>
       </c>
       <c r="AG89">
-        <v>0.1734360573223446</v>
+        <v>0.8682687866867136</v>
       </c>
       <c r="AH89">
-        <v>-0.08098069371162318</v>
+        <v>0.3987754670851489</v>
       </c>
       <c r="AI89">
         <v>0.02016228132551838</v>
@@ -18928,19 +18928,19 @@
         <v>0.1474233616151251</v>
       </c>
       <c r="F90">
-        <v>-0.5710840481119954</v>
+        <v>-0.9325044820990825</v>
       </c>
       <c r="G90">
-        <v>2.066951096654791</v>
+        <v>1.962975174596518</v>
       </c>
       <c r="H90">
-        <v>-0.07257693485171357</v>
+        <v>-0.1937905802595867</v>
       </c>
       <c r="I90">
-        <v>-0.09300113559816051</v>
+        <v>0.0352486154091159</v>
       </c>
       <c r="J90">
-        <v>-0.7708212781156289</v>
+        <v>-0.5972016026294857</v>
       </c>
       <c r="K90">
         <v>-2.150406454214997</v>
@@ -19000,19 +19000,19 @@
         <v>-0.08522072498499431</v>
       </c>
       <c r="AD90">
-        <v>-1.363807047560512</v>
+        <v>-1.63700554234955</v>
       </c>
       <c r="AE90">
-        <v>0.2978442325920183</v>
+        <v>0.443811278611979</v>
       </c>
       <c r="AF90">
-        <v>-0.08760228620364774</v>
+        <v>-0.03236263196617684</v>
       </c>
       <c r="AG90">
-        <v>0.1506417934398214</v>
+        <v>-0.09832119987758162</v>
       </c>
       <c r="AH90">
-        <v>-0.04529608939880819</v>
+        <v>0.1393792394915134</v>
       </c>
       <c r="AI90">
         <v>1.135480229099373</v>
@@ -19135,19 +19135,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F91">
-        <v>-0.1246047183253094</v>
+        <v>-0.3257657755470357</v>
       </c>
       <c r="G91">
-        <v>0.9645777909981517</v>
+        <v>0.9440083427800103</v>
       </c>
       <c r="H91">
-        <v>-1.162979837308436</v>
+        <v>-1.132126708432824</v>
       </c>
       <c r="I91">
-        <v>-0.07068594650476319</v>
+        <v>0.2581946832092155</v>
       </c>
       <c r="J91">
-        <v>-1.269370443480498</v>
+        <v>-1.281460022155705</v>
       </c>
       <c r="K91">
         <v>-2.691627050387673</v>
@@ -19207,19 +19207,19 @@
         <v>0.8211765860120505</v>
       </c>
       <c r="AD91">
-        <v>-0.01395245744377593</v>
+        <v>0.4473631034756956</v>
       </c>
       <c r="AE91">
-        <v>1.470055994683394</v>
+        <v>1.517998559328855</v>
       </c>
       <c r="AF91">
-        <v>0.5633858812986579</v>
+        <v>0.5099583390328719</v>
       </c>
       <c r="AG91">
-        <v>-0.3691143242832799</v>
+        <v>0.1881064265453948</v>
       </c>
       <c r="AH91">
-        <v>-0.03501470545789274</v>
+        <v>-0.3442350343005041</v>
       </c>
       <c r="AI91">
         <v>0.05675605867493566</v>
@@ -19342,19 +19342,19 @@
         <v>-0.08070871199348881</v>
       </c>
       <c r="F92">
-        <v>0.05469696248486669</v>
+        <v>-0.0209843201867501</v>
       </c>
       <c r="G92">
-        <v>-0.7606039366499743</v>
+        <v>-0.5820984583730552</v>
       </c>
       <c r="H92">
-        <v>1.57749345608154</v>
+        <v>1.7022705192609</v>
       </c>
       <c r="I92">
-        <v>0.5344593171895046</v>
+        <v>0.6919060122491176</v>
       </c>
       <c r="J92">
-        <v>-0.6925311994236929</v>
+        <v>-0.5563917399459763</v>
       </c>
       <c r="K92">
         <v>-1.413513945850142</v>
@@ -19414,19 +19414,19 @@
         <v>0.6400981559392454</v>
       </c>
       <c r="AD92">
-        <v>0.5929447250739524</v>
+        <v>0.4921181861950761</v>
       </c>
       <c r="AE92">
-        <v>0.1698482499294495</v>
+        <v>0.05570628631378063</v>
       </c>
       <c r="AF92">
-        <v>-1.092362562764272</v>
+        <v>-1.142743106294468</v>
       </c>
       <c r="AG92">
-        <v>1.065872056706864</v>
+        <v>-0.08466200574039766</v>
       </c>
       <c r="AH92">
-        <v>-0.2927801705763346</v>
+        <v>1.095142140602357</v>
       </c>
       <c r="AI92">
         <v>0.118374542512976</v>
@@ -19549,19 +19549,19 @@
         <v>-0.1003120399345884</v>
       </c>
       <c r="F93">
-        <v>0.7917602619681644</v>
+        <v>0.5786641821448927</v>
       </c>
       <c r="G93">
-        <v>0.5886314153410388</v>
+        <v>0.7802227862888566</v>
       </c>
       <c r="H93">
-        <v>0.07592619622261687</v>
+        <v>0.1405664661971158</v>
       </c>
       <c r="I93">
-        <v>-0.0540470563772707</v>
+        <v>0.04289949784622699</v>
       </c>
       <c r="J93">
-        <v>-0.1499856208084887</v>
+        <v>-0.3239805468814412</v>
       </c>
       <c r="K93">
         <v>2.543302402702652</v>
@@ -19621,19 +19621,19 @@
         <v>-0.1687404523091279</v>
       </c>
       <c r="AD93">
-        <v>0.3323094948120652</v>
+        <v>0.5968966193351612</v>
       </c>
       <c r="AE93">
-        <v>-0.3616990807514001</v>
+        <v>-0.3669706302003547</v>
       </c>
       <c r="AF93">
-        <v>0.2664056317546476</v>
+        <v>0.3535046578134932</v>
       </c>
       <c r="AG93">
-        <v>0.2469755735639602</v>
+        <v>-0.6866483959985125</v>
       </c>
       <c r="AH93">
-        <v>-0.1453917515340379</v>
+        <v>0.07683727533045846</v>
       </c>
       <c r="AI93">
         <v>2.064644730358687</v>
@@ -19756,19 +19756,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F94">
-        <v>-1.070301975371745</v>
+        <v>-1.596934778754652</v>
       </c>
       <c r="G94">
-        <v>3.619332824957266</v>
+        <v>3.35709240579969</v>
       </c>
       <c r="H94">
-        <v>0.1955205966614184</v>
+        <v>-0.1212896829524497</v>
       </c>
       <c r="I94">
-        <v>0.7466327381549634</v>
+        <v>0.660691849845101</v>
       </c>
       <c r="J94">
-        <v>-0.5212815897725979</v>
+        <v>0.2040809671593031</v>
       </c>
       <c r="K94">
         <v>-1.317713066018692</v>
@@ -19828,19 +19828,19 @@
         <v>-0.3716394995146747</v>
       </c>
       <c r="AD94">
-        <v>-1.721706286654919</v>
+        <v>-2.653907063154613</v>
       </c>
       <c r="AE94">
-        <v>-0.447882040745247</v>
+        <v>-0.305519548680745</v>
       </c>
       <c r="AF94">
-        <v>-0.005069204250680803</v>
+        <v>-0.05722070991805184</v>
       </c>
       <c r="AG94">
-        <v>0.09253860263297561</v>
+        <v>0.5680793711202348</v>
       </c>
       <c r="AH94">
-        <v>-0.2055344396990527</v>
+        <v>0.2503804452343794</v>
       </c>
       <c r="AI94">
         <v>-0.192259349004995</v>
@@ -19963,19 +19963,19 @@
         <v>0.1825944074282326</v>
       </c>
       <c r="F95">
-        <v>-3.418664989026673</v>
+        <v>-2.823901924993474</v>
       </c>
       <c r="G95">
-        <v>-3.497789422533778</v>
+        <v>-3.995558351595295</v>
       </c>
       <c r="H95">
-        <v>-0.3398793453520426</v>
+        <v>-0.232350181132409</v>
       </c>
       <c r="I95">
-        <v>1.156909096577565</v>
+        <v>1.291945952700564</v>
       </c>
       <c r="J95">
-        <v>-0.6196224059959825</v>
+        <v>-0.366071244487071</v>
       </c>
       <c r="K95">
         <v>-8.460697984123838</v>
@@ -20035,19 +20035,19 @@
         <v>0.6306041574108109</v>
       </c>
       <c r="AD95">
-        <v>-3.295169397248583</v>
+        <v>-4.055625448970792</v>
       </c>
       <c r="AE95">
-        <v>0.3980234258526965</v>
+        <v>0.727212667311419</v>
       </c>
       <c r="AF95">
-        <v>0.4947339978116505</v>
+        <v>0.5777998283126438</v>
       </c>
       <c r="AG95">
-        <v>-0.1324604739013725</v>
+        <v>0.01230376907187189</v>
       </c>
       <c r="AH95">
-        <v>0.1763492597597761</v>
+        <v>-0.1399008280072332</v>
       </c>
       <c r="AI95">
         <v>-0.235757966991814</v>
@@ -20170,19 +20170,19 @@
         <v>0.2918948368373444</v>
       </c>
       <c r="F96">
-        <v>-0.4276175345208242</v>
+        <v>-0.4533153361201251</v>
       </c>
       <c r="G96">
-        <v>-0.3958081600707267</v>
+        <v>-0.4040012318102015</v>
       </c>
       <c r="H96">
-        <v>-0.332153854720753</v>
+        <v>-0.2487152772075421</v>
       </c>
       <c r="I96">
-        <v>0.02369071709927249</v>
+        <v>0.2439281331077846</v>
       </c>
       <c r="J96">
-        <v>-0.8418003131667815</v>
+        <v>-0.8415088011635662</v>
       </c>
       <c r="K96">
         <v>-0.7216998801426131</v>
@@ -20242,19 +20242,19 @@
         <v>0.7587219812103555</v>
       </c>
       <c r="AD96">
-        <v>-0.4157037204060638</v>
+        <v>-0.8743344194233964</v>
       </c>
       <c r="AE96">
-        <v>-0.008266264980580251</v>
+        <v>-0.07475156435196084</v>
       </c>
       <c r="AF96">
-        <v>-1.407701408655081</v>
+        <v>-1.414185814056744</v>
       </c>
       <c r="AG96">
-        <v>0.6711075325041121</v>
+        <v>-0.4793999028598904</v>
       </c>
       <c r="AH96">
-        <v>0.2610289652498488</v>
+        <v>0.5940010338478517</v>
       </c>
       <c r="AI96">
         <v>-0.6570907692225348</v>
@@ -20377,19 +20377,19 @@
         <v>-0.1005508099517721</v>
       </c>
       <c r="F97">
-        <v>1.645160795385248</v>
+        <v>1.637373871265473</v>
       </c>
       <c r="G97">
-        <v>-0.7363395826578573</v>
+        <v>-0.4321866693566356</v>
       </c>
       <c r="H97">
-        <v>-2.39982263849059</v>
+        <v>-2.134096375506274</v>
       </c>
       <c r="I97">
-        <v>-0.4929708752655481</v>
+        <v>-0.2687844088418478</v>
       </c>
       <c r="J97">
-        <v>0.08117245808525364</v>
+        <v>-0.6577831179576649</v>
       </c>
       <c r="K97">
         <v>3.122754726341261</v>
@@ -20449,19 +20449,19 @@
         <v>0.07772467161292469</v>
       </c>
       <c r="AD97">
-        <v>-0.3832915375497994</v>
+        <v>-0.7072816612946031</v>
       </c>
       <c r="AE97">
-        <v>-1.479599576437648</v>
+        <v>-1.457388852904361</v>
       </c>
       <c r="AF97">
-        <v>-0.2784793457877385</v>
+        <v>-0.1395101521938826</v>
       </c>
       <c r="AG97">
-        <v>0.1808558717697856</v>
+        <v>-0.6308132885255171</v>
       </c>
       <c r="AH97">
-        <v>0.1242700169201102</v>
+        <v>0.03686864534501694</v>
       </c>
       <c r="AI97">
         <v>3.882814846273908</v>
@@ -20584,19 +20584,19 @@
         <v>0.1430269808884867</v>
       </c>
       <c r="F98">
-        <v>-1.832261377962032</v>
+        <v>-1.656582632773973</v>
       </c>
       <c r="G98">
-        <v>-1.051864202755759</v>
+        <v>-1.353338401359978</v>
       </c>
       <c r="H98">
-        <v>-1.724097531157228</v>
+        <v>-1.655339263753036</v>
       </c>
       <c r="I98">
-        <v>-0.04953879074951772</v>
+        <v>0.1641928044943325</v>
       </c>
       <c r="J98">
-        <v>-0.5746053264952274</v>
+        <v>-0.7576371110269341</v>
       </c>
       <c r="K98">
         <v>-7.557595216692209</v>
@@ -20656,19 +20656,19 @@
         <v>0.4430886173158241</v>
       </c>
       <c r="AD98">
-        <v>-2.125115052958473</v>
+        <v>-2.558486505210728</v>
       </c>
       <c r="AE98">
-        <v>0.6224720586817922</v>
+        <v>0.8077572347073689</v>
       </c>
       <c r="AF98">
-        <v>-0.07672864120976408</v>
+        <v>-0.02016838243535068</v>
       </c>
       <c r="AG98">
-        <v>-0.6261707341440231</v>
+        <v>-0.3722814918503374</v>
       </c>
       <c r="AH98">
-        <v>-0.1406533659755011</v>
+        <v>-0.7381645980166439</v>
       </c>
       <c r="AI98">
         <v>-1.388870331320306</v>
@@ -20791,19 +20791,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F99">
-        <v>1.930100276628201</v>
+        <v>1.761533440960938</v>
       </c>
       <c r="G99">
-        <v>0.008555949151668449</v>
+        <v>0.4094235477726855</v>
       </c>
       <c r="H99">
-        <v>0.4117517459569114</v>
+        <v>0.5199343678823256</v>
       </c>
       <c r="I99">
-        <v>1.562072615884629</v>
+        <v>1.241228927176711</v>
       </c>
       <c r="J99">
-        <v>1.47632327553297</v>
+        <v>1.573204113036838</v>
       </c>
       <c r="K99">
         <v>0.6511947626242107</v>
@@ -20863,19 +20863,19 @@
         <v>0.6825276059207279</v>
       </c>
       <c r="AD99">
-        <v>1.009305175056198</v>
+        <v>1.635219893215939</v>
       </c>
       <c r="AE99">
-        <v>1.276115534187383</v>
+        <v>1.166565195005742</v>
       </c>
       <c r="AF99">
-        <v>-0.2025233296237564</v>
+        <v>-0.251973269100949</v>
       </c>
       <c r="AG99">
-        <v>0.0512696830886087</v>
+        <v>-0.4275032603491461</v>
       </c>
       <c r="AH99">
-        <v>0.2703774252599733</v>
+        <v>-0.05695657462752957</v>
       </c>
       <c r="AI99">
         <v>-1.288213399366346</v>
@@ -20998,19 +20998,19 @@
         <v>0.1335014893141034</v>
       </c>
       <c r="F100">
-        <v>-0.187276288702045</v>
+        <v>-0.3608070530683505</v>
       </c>
       <c r="G100">
-        <v>0.9542782588886756</v>
+        <v>0.897771395603162</v>
       </c>
       <c r="H100">
-        <v>-1.10711414131642</v>
+        <v>-1.135422286108447</v>
       </c>
       <c r="I100">
-        <v>-1.446160349885028</v>
+        <v>-1.358547860689467</v>
       </c>
       <c r="J100">
-        <v>0.009237175671049203</v>
+        <v>-0.4695716377686636</v>
       </c>
       <c r="K100">
         <v>1.80159707247778</v>
@@ -21070,19 +21070,19 @@
         <v>-0.4411152003527213</v>
       </c>
       <c r="AD100">
-        <v>0.1367163615411768</v>
+        <v>0.6179723193932795</v>
       </c>
       <c r="AE100">
-        <v>1.3238343799334</v>
+        <v>1.335862999168059</v>
       </c>
       <c r="AF100">
-        <v>0.1572231219028959</v>
+        <v>0.1455340978196162</v>
       </c>
       <c r="AG100">
-        <v>0.1814963926863884</v>
+        <v>-0.3028005121457926</v>
       </c>
       <c r="AH100">
-        <v>-0.06529777993933691</v>
+        <v>0.1049380427968892</v>
       </c>
       <c r="AI100">
         <v>-0.7216851385888114</v>
@@ -21205,19 +21205,19 @@
         <v>-0.5721820705261088</v>
       </c>
       <c r="F101">
-        <v>0.3629987833044832</v>
+        <v>0.0432422428054146</v>
       </c>
       <c r="G101">
-        <v>1.282188850755241</v>
+        <v>1.402186009374423</v>
       </c>
       <c r="H101">
-        <v>0.74776159298498</v>
+        <v>0.7184649366669672</v>
       </c>
       <c r="I101">
-        <v>-0.1401451196839163</v>
+        <v>-0.1107572573225633</v>
       </c>
       <c r="J101">
-        <v>-0.130542265429455</v>
+        <v>-0.1506341786927839</v>
       </c>
       <c r="K101">
         <v>1.341656992233995</v>
@@ -21277,19 +21277,19 @@
         <v>-0.3193197099667234</v>
       </c>
       <c r="AD101">
-        <v>1.004868971741891</v>
+        <v>1.159494390965403</v>
       </c>
       <c r="AE101">
-        <v>-1.488225390892863</v>
+        <v>-1.56168509136938</v>
       </c>
       <c r="AF101">
-        <v>0.1267352828913347</v>
+        <v>0.2347486804676212</v>
       </c>
       <c r="AG101">
-        <v>0.7407415155937074</v>
+        <v>-0.6008918899473772</v>
       </c>
       <c r="AH101">
-        <v>-0.1816675164894583</v>
+        <v>0.6118167187274236</v>
       </c>
       <c r="AI101">
         <v>-0.1269092211572307</v>
@@ -21412,19 +21412,19 @@
         <v>-0.1818777352808466</v>
       </c>
       <c r="F102">
-        <v>0.6804496115905426</v>
+        <v>0.4556568141391863</v>
       </c>
       <c r="G102">
-        <v>0.3368466682233791</v>
+        <v>0.5669134124765902</v>
       </c>
       <c r="H102">
-        <v>1.272965869888173</v>
+        <v>1.32718036349408</v>
       </c>
       <c r="I102">
-        <v>0.8838937559258615</v>
+        <v>0.848792831600378</v>
       </c>
       <c r="J102">
-        <v>0.08304711639833484</v>
+        <v>0.2567098814037919</v>
       </c>
       <c r="K102">
         <v>0.1771029374522819</v>
@@ -21484,19 +21484,19 @@
         <v>-0.4679227487037521</v>
       </c>
       <c r="AD102">
-        <v>2.764313017376976</v>
+        <v>3.927652216637203</v>
       </c>
       <c r="AE102">
-        <v>1.363948432184383</v>
+        <v>1.078263939772267</v>
       </c>
       <c r="AF102">
-        <v>-0.4257967514197358</v>
+        <v>-0.5053077845445557</v>
       </c>
       <c r="AG102">
-        <v>0.204368389669211</v>
+        <v>-0.7216397887957701</v>
       </c>
       <c r="AH102">
-        <v>-0.01400761913076093</v>
+        <v>0.02414611825477575</v>
       </c>
       <c r="AI102">
         <v>-0.7148128122816904</v>
@@ -21619,19 +21619,19 @@
         <v>-0.1699797477895691</v>
       </c>
       <c r="F103">
-        <v>1.132423769824054</v>
+        <v>2.741253979505393</v>
       </c>
       <c r="G103">
-        <v>-0.6150047325801672</v>
+        <v>-1.367138133260293</v>
       </c>
       <c r="H103">
-        <v>-0.8837532785991097</v>
+        <v>-1.574669848566261</v>
       </c>
       <c r="I103">
-        <v>-1.241370947156764</v>
+        <v>-1.798442048982585</v>
       </c>
       <c r="J103">
-        <v>0.1662520414646139</v>
+        <v>1.389803746554801</v>
       </c>
       <c r="K103">
         <v>2.539066193697079</v>
@@ -21691,19 +21691,19 @@
         <v>-0.3602798494184852</v>
       </c>
       <c r="AD103">
-        <v>-0.5087714140610166</v>
+        <v>-1.159147976286181</v>
       </c>
       <c r="AE103">
-        <v>-1.594481448034846</v>
+        <v>-1.597779214755981</v>
       </c>
       <c r="AF103">
-        <v>-0.7895132503065229</v>
+        <v>-0.7076015993954403</v>
       </c>
       <c r="AG103">
-        <v>-0.05812960522941107</v>
+        <v>-0.22352978106675</v>
       </c>
       <c r="AH103">
-        <v>-0.07006020856004137</v>
+        <v>-0.09670402475406556</v>
       </c>
       <c r="AI103">
         <v>0.5238647087282282</v>
@@ -21826,19 +21826,19 @@
         <v>0.1349669495563162</v>
       </c>
       <c r="F104">
-        <v>1.644523702968532</v>
+        <v>1.467773172590264</v>
       </c>
       <c r="G104">
-        <v>0.5681456873498911</v>
+        <v>0.8208277740124917</v>
       </c>
       <c r="H104">
-        <v>-2.648598614004396</v>
+        <v>-2.479390293983588</v>
       </c>
       <c r="I104">
-        <v>-0.8115316553903672</v>
+        <v>-0.6037193407700902</v>
       </c>
       <c r="J104">
-        <v>0.09231182555388634</v>
+        <v>-0.6646821003601556</v>
       </c>
       <c r="K104">
         <v>1.316737385235071</v>
@@ -21898,19 +21898,19 @@
         <v>-0.3724474102241012</v>
       </c>
       <c r="AD104">
-        <v>1.379598761762736</v>
+        <v>2.275298614316885</v>
       </c>
       <c r="AE104">
-        <v>-0.2935400518017238</v>
+        <v>-0.2909740039308974</v>
       </c>
       <c r="AF104">
-        <v>1.123177686298596</v>
+        <v>1.226947509441179</v>
       </c>
       <c r="AG104">
-        <v>0.2686921031360277</v>
+        <v>-0.2110324928559681</v>
       </c>
       <c r="AH104">
-        <v>-0.2355295591782887</v>
+        <v>0.2106431158382072</v>
       </c>
       <c r="AI104">
         <v>0.7302952766360657</v>
@@ -22033,19 +22033,19 @@
         <v>0.1305705688296778</v>
       </c>
       <c r="F105">
-        <v>1.074642807562157</v>
+        <v>0.8965654185062839</v>
       </c>
       <c r="G105">
-        <v>0.4995260444883087</v>
+        <v>0.7039168855041456</v>
       </c>
       <c r="H105">
-        <v>-0.8665513271984839</v>
+        <v>-0.7745284551838525</v>
       </c>
       <c r="I105">
-        <v>-0.9625802735277982</v>
+        <v>-0.8823003224452476</v>
       </c>
       <c r="J105">
-        <v>0.3647422673228788</v>
+        <v>-0.2745462707279265</v>
       </c>
       <c r="K105">
         <v>1.723508036217847</v>
@@ -22105,19 +22105,19 @@
         <v>-0.2689217570391493</v>
       </c>
       <c r="AD105">
-        <v>-0.2165011323841212</v>
+        <v>-0.7336695322654238</v>
       </c>
       <c r="AE105">
-        <v>-0.3132693576233153</v>
+        <v>-0.3791687156354721</v>
       </c>
       <c r="AF105">
-        <v>-0.6292010679917693</v>
+        <v>-0.7169134293277174</v>
       </c>
       <c r="AG105">
-        <v>-0.6592695267029259</v>
+        <v>0.3703960754468226</v>
       </c>
       <c r="AH105">
-        <v>0.221749392959666</v>
+        <v>-0.5789767243871993</v>
       </c>
       <c r="AI105">
         <v>-1.023893767038122</v>
@@ -22240,19 +22240,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F106">
-        <v>-2.208612861262733</v>
+        <v>-2.156118088734448</v>
       </c>
       <c r="G106">
-        <v>0.01734915779672039</v>
+        <v>-0.3696631488073301</v>
       </c>
       <c r="H106">
-        <v>-0.1159766192168915</v>
+        <v>-0.2447933380883779</v>
       </c>
       <c r="I106">
-        <v>-0.4065383303726395</v>
+        <v>-0.545326652103987</v>
       </c>
       <c r="J106">
-        <v>0.5124102236247412</v>
+        <v>0.4604744585652096</v>
       </c>
       <c r="K106">
         <v>-1.576175590572001</v>
@@ -22312,19 +22312,19 @@
         <v>-0.52706616374446</v>
       </c>
       <c r="AD106">
-        <v>-2.155117117570998</v>
+        <v>-3.738535773507726</v>
       </c>
       <c r="AE106">
-        <v>-1.059200427339337</v>
+        <v>-1.008603701931471</v>
       </c>
       <c r="AF106">
-        <v>-1.290988626194469</v>
+        <v>-1.350433410540777</v>
       </c>
       <c r="AG106">
-        <v>0.8634370148858768</v>
+        <v>0.1520082337267959</v>
       </c>
       <c r="AH106">
-        <v>0.1765802823489862</v>
+        <v>0.9515112556827708</v>
       </c>
       <c r="AI106">
         <v>1.288303430344284</v>
@@ -22447,19 +22447,19 @@
         <v>0.5523269263319955</v>
       </c>
       <c r="F107">
-        <v>0.3899569824668406</v>
+        <v>0.2378445583759018</v>
       </c>
       <c r="G107">
-        <v>0.6584555926158898</v>
+        <v>0.7344592433906477</v>
       </c>
       <c r="H107">
-        <v>0.0170560409164442</v>
+        <v>0.005082582244150161</v>
       </c>
       <c r="I107">
-        <v>-0.3947867408263688</v>
+        <v>-0.4119380681193259</v>
       </c>
       <c r="J107">
-        <v>0.1697906910331791</v>
+        <v>0.03215989519263893</v>
       </c>
       <c r="K107">
         <v>-2.352163185277147</v>
@@ -22519,19 +22519,19 @@
         <v>-0.2389480317834212</v>
       </c>
       <c r="AD107">
-        <v>0.5581011579811478</v>
+        <v>0.6218962530787988</v>
       </c>
       <c r="AE107">
-        <v>1.503763092568728</v>
+        <v>1.389965221340515</v>
       </c>
       <c r="AF107">
-        <v>-0.791989086801595</v>
+        <v>-0.9830261048827444</v>
       </c>
       <c r="AG107">
-        <v>-0.05135279649343313</v>
+        <v>0.7559818185400591</v>
       </c>
       <c r="AH107">
-        <v>0.1852244493097013</v>
+        <v>0.1465933695133943</v>
       </c>
       <c r="AI107">
         <v>-0.9316233285907336</v>
@@ -22654,19 +22654,19 @@
         <v>-0.101660297563713</v>
       </c>
       <c r="F108">
-        <v>0.4234646542086403</v>
+        <v>0.3250048583619537</v>
       </c>
       <c r="G108">
-        <v>0.1127816933326863</v>
+        <v>0.1984180142623376</v>
       </c>
       <c r="H108">
-        <v>-1.840683640569892</v>
+        <v>-1.702536811385458</v>
       </c>
       <c r="I108">
-        <v>-0.401981392010633</v>
+        <v>-0.1094446155990572</v>
       </c>
       <c r="J108">
-        <v>-0.6138424217070251</v>
+        <v>-1.042254861171988</v>
       </c>
       <c r="K108">
         <v>2.289802970562414</v>
@@ -22726,19 +22726,19 @@
         <v>-0.3856394568239654</v>
       </c>
       <c r="AD108">
-        <v>1.350769212799546</v>
+        <v>1.850278032570236</v>
       </c>
       <c r="AE108">
-        <v>0.2081325440397148</v>
+        <v>0.07727184371704048</v>
       </c>
       <c r="AF108">
-        <v>-0.1291953681347499</v>
+        <v>-0.1429576046639812</v>
       </c>
       <c r="AG108">
-        <v>-0.0168940246004872</v>
+        <v>-0.3011179928396412</v>
       </c>
       <c r="AH108">
-        <v>-0.1283421373169</v>
+        <v>-0.09617956436292063</v>
       </c>
       <c r="AI108">
         <v>-0.8693480635500979</v>
@@ -22861,19 +22861,19 @@
         <v>-0.6535160949187455</v>
       </c>
       <c r="F109">
-        <v>1.179248584021267</v>
+        <v>0.9260939940822822</v>
       </c>
       <c r="G109">
-        <v>0.6446467680975099</v>
+        <v>0.9065044498398008</v>
       </c>
       <c r="H109">
-        <v>-0.6627749869384744</v>
+        <v>-0.5247135950674866</v>
       </c>
       <c r="I109">
-        <v>1.000068465876889</v>
+        <v>1.233245924504957</v>
       </c>
       <c r="J109">
-        <v>-0.7014884927668557</v>
+        <v>-0.6841651801181988</v>
       </c>
       <c r="K109">
         <v>1.790507287049543</v>
@@ -22933,19 +22933,19 @@
         <v>0.5360829887339736</v>
       </c>
       <c r="AD109">
-        <v>3.07995742707377</v>
+        <v>4.149102861662582</v>
       </c>
       <c r="AE109">
-        <v>1.949360503257368</v>
+        <v>1.581996510879243</v>
       </c>
       <c r="AF109">
-        <v>-1.078363214546839</v>
+        <v>-1.267990350844383</v>
       </c>
       <c r="AG109">
-        <v>0.1732126121323299</v>
+        <v>-0.2229748320282698</v>
       </c>
       <c r="AH109">
-        <v>0.1309595508377981</v>
+        <v>0.1257260389208001</v>
       </c>
       <c r="AI109">
         <v>-0.8198378124865805</v>
@@ -23068,19 +23068,19 @@
         <v>-0.101660297563713</v>
       </c>
       <c r="F110">
-        <v>-1.497844692880546</v>
+        <v>-1.315963592724809</v>
       </c>
       <c r="G110">
-        <v>-1.741409930408131</v>
+        <v>-1.871919621909736</v>
       </c>
       <c r="H110">
-        <v>0.9395918848526024</v>
+        <v>1.001666185473055</v>
       </c>
       <c r="I110">
-        <v>0.1993933661656235</v>
+        <v>0.07676389443468884</v>
       </c>
       <c r="J110">
-        <v>0.6855542411499267</v>
+        <v>0.5603310920416851</v>
       </c>
       <c r="K110">
         <v>-5.182944760151806</v>
@@ -23140,19 +23140,19 @@
         <v>1.947787925409857</v>
       </c>
       <c r="AD110">
-        <v>-2.722560154132829</v>
+        <v>-3.880700381670974</v>
       </c>
       <c r="AE110">
-        <v>0.5752747169622118</v>
+        <v>0.7095746406979796</v>
       </c>
       <c r="AF110">
-        <v>-1.345050324794683</v>
+        <v>-1.38258903456348</v>
       </c>
       <c r="AG110">
-        <v>-0.4142801188265118</v>
+        <v>0.1116368649974766</v>
       </c>
       <c r="AH110">
-        <v>-0.01450089418288265</v>
+        <v>-0.3788735812984954</v>
       </c>
       <c r="AI110">
         <v>-0.7969446698899028</v>
@@ -23275,19 +23275,19 @@
         <v>-0.1023930276848194</v>
       </c>
       <c r="F111">
-        <v>1.243856572947172</v>
+        <v>0.9499486143437919</v>
       </c>
       <c r="G111">
-        <v>0.6285176514966959</v>
+        <v>0.9623261890490474</v>
       </c>
       <c r="H111">
-        <v>1.788358616151744</v>
+        <v>1.832709722300429</v>
       </c>
       <c r="I111">
-        <v>1.639524170703658</v>
+        <v>1.570675034837446</v>
       </c>
       <c r="J111">
-        <v>-0.1531200438461732</v>
+        <v>0.4111491372431054</v>
       </c>
       <c r="K111">
         <v>2.673491410676559</v>
@@ -23347,19 +23347,19 @@
         <v>0.06934911280024753</v>
       </c>
       <c r="AD111">
-        <v>0.6600466295955367</v>
+        <v>1.272345915491485</v>
       </c>
       <c r="AE111">
-        <v>0.6196069414900999</v>
+        <v>0.6296342989449679</v>
       </c>
       <c r="AF111">
-        <v>1.055226745978905</v>
+        <v>1.053682604247153</v>
       </c>
       <c r="AG111">
-        <v>0.8427323602078718</v>
+        <v>-0.2098112720040417</v>
       </c>
       <c r="AH111">
-        <v>-0.09989706149189553</v>
+        <v>0.7935781765437613</v>
       </c>
       <c r="AI111">
         <v>-0.9006779061367647</v>
@@ -23482,19 +23482,19 @@
         <v>-1.361720004452275</v>
       </c>
       <c r="F112">
-        <v>0.2767921259678151</v>
+        <v>0.3012182429146693</v>
       </c>
       <c r="G112">
-        <v>-2.165743352758865</v>
+        <v>-1.810345462090538</v>
       </c>
       <c r="H112">
-        <v>3.249109740268692</v>
+        <v>3.513270825247824</v>
       </c>
       <c r="I112">
-        <v>0.3061817999681476</v>
+        <v>0.5900920834842094</v>
       </c>
       <c r="J112">
-        <v>-0.9377050188427103</v>
+        <v>-1.032924993234864</v>
       </c>
       <c r="K112">
         <v>2.494391554069116</v>
@@ -23554,19 +23554,19 @@
         <v>-0.7054043090511144</v>
       </c>
       <c r="AD112">
-        <v>3.160758353949882</v>
+        <v>4.391311432571693</v>
       </c>
       <c r="AE112">
-        <v>-0.1711048009799861</v>
+        <v>-0.4146252407228338</v>
       </c>
       <c r="AF112">
-        <v>0.5094599009276419</v>
+        <v>0.5196693056674656</v>
       </c>
       <c r="AG112">
-        <v>-0.151988306519739</v>
+        <v>-0.4732247776225486</v>
       </c>
       <c r="AH112">
-        <v>-0.05837003313149804</v>
+        <v>-0.2888491356561148</v>
       </c>
       <c r="AI112">
         <v>1.147387834770622</v>
@@ -23689,19 +23689,19 @@
         <v>0.2133690725147016</v>
       </c>
       <c r="F113">
-        <v>0.990951003663656</v>
+        <v>0.7522337819280968</v>
       </c>
       <c r="G113">
-        <v>1.190257815226943</v>
+        <v>1.31953590901206</v>
       </c>
       <c r="H113">
-        <v>-1.744636834152962</v>
+        <v>-1.704400168239032</v>
       </c>
       <c r="I113">
-        <v>0.06687820881273975</v>
+        <v>0.1110046081568407</v>
       </c>
       <c r="J113">
-        <v>0.1983964965813689</v>
+        <v>-0.04315913615959285</v>
       </c>
       <c r="K113">
         <v>-1.861245236023531</v>
@@ -23761,19 +23761,19 @@
         <v>-0.6595429945754423</v>
       </c>
       <c r="AD113">
-        <v>-0.5215846957571713</v>
+        <v>-0.9621809133406313</v>
       </c>
       <c r="AE113">
-        <v>-0.399390430560085</v>
+        <v>-0.417099384825635</v>
       </c>
       <c r="AF113">
-        <v>-0.7324887258054692</v>
+        <v>-0.7258635827898903</v>
       </c>
       <c r="AG113">
-        <v>-0.3731795283021782</v>
+        <v>-0.07534042866195659</v>
       </c>
       <c r="AH113">
-        <v>-0.07080912061083514</v>
+        <v>-0.3957365234083445</v>
       </c>
       <c r="AI113">
         <v>-0.7678688078788797</v>
@@ -23896,19 +23896,19 @@
         <v>-0.07394205729238756</v>
       </c>
       <c r="F114">
-        <v>-0.9709451897192906</v>
+        <v>-0.4176812503114622</v>
       </c>
       <c r="G114">
-        <v>-2.152466353163687</v>
+        <v>-2.443149718721302</v>
       </c>
       <c r="H114">
-        <v>-3.195919810414642</v>
+        <v>-3.049959003110462</v>
       </c>
       <c r="I114">
-        <v>1.434040046430801</v>
+        <v>1.814873036544138</v>
       </c>
       <c r="J114">
-        <v>-1.586177073430586</v>
+        <v>-1.252825712987117</v>
       </c>
       <c r="K114">
         <v>-6.24308103829848</v>
@@ -23968,19 +23968,19 @@
         <v>0.2165164646827436</v>
       </c>
       <c r="AD114">
-        <v>-2.962776196931117</v>
+        <v>-4.178296933073032</v>
       </c>
       <c r="AE114">
-        <v>-0.2849790629476541</v>
+        <v>-0.08696329460464811</v>
       </c>
       <c r="AF114">
-        <v>-0.8289901858238603</v>
+        <v>-0.7835304057991161</v>
       </c>
       <c r="AG114">
-        <v>-0.2227994763780034</v>
+        <v>0.02467283927057484</v>
       </c>
       <c r="AH114">
-        <v>0.1127718614670426</v>
+        <v>-0.2084207721927002</v>
       </c>
       <c r="AI114">
         <v>4.727909130632121</v>
@@ -24103,19 +24103,19 @@
         <v>0.1496215519784443</v>
       </c>
       <c r="F115">
-        <v>-2.487430439008234</v>
+        <v>-2.172300290906855</v>
       </c>
       <c r="G115">
-        <v>-2.886128952316267</v>
+        <v>-3.079887043953754</v>
       </c>
       <c r="H115">
-        <v>3.085246496578513</v>
+        <v>3.145540078697891</v>
       </c>
       <c r="I115">
-        <v>-3.051003599846906</v>
+        <v>-2.765859582924821</v>
       </c>
       <c r="J115">
-        <v>-1.45399549872841</v>
+        <v>-1.698499290452875</v>
       </c>
       <c r="K115">
         <v>-7.745781990408358</v>
@@ -24175,19 +24175,19 @@
         <v>0.4039306923847295</v>
       </c>
       <c r="AD115">
-        <v>-0.8279085207129887</v>
+        <v>-0.6658901709920813</v>
       </c>
       <c r="AE115">
-        <v>0.8076829161138082</v>
+        <v>0.931998621059324</v>
       </c>
       <c r="AF115">
-        <v>0.4060395417676167</v>
+        <v>0.457166685686248</v>
       </c>
       <c r="AG115">
-        <v>0.5031548386232529</v>
+        <v>-0.3163485870516001</v>
       </c>
       <c r="AH115">
-        <v>-0.01110007055404521</v>
+        <v>0.4337327613896206</v>
       </c>
       <c r="AI115">
         <v>-0.5364076640042804</v>
@@ -24310,19 +24310,19 @@
         <v>0.5685770492724284</v>
       </c>
       <c r="F116">
-        <v>-1.655089130246827</v>
+        <v>-1.495636129385886</v>
       </c>
       <c r="G116">
-        <v>-0.9388275718153141</v>
+        <v>-1.192265329226655</v>
       </c>
       <c r="H116">
-        <v>0.3092276121503665</v>
+        <v>0.2544488310818924</v>
       </c>
       <c r="I116">
-        <v>-1.283646716538289</v>
+        <v>-1.427690294140877</v>
       </c>
       <c r="J116">
-        <v>0.6580409740092108</v>
+        <v>0.3831158208833031</v>
       </c>
       <c r="K116">
         <v>2.288302367476204</v>
@@ -24382,19 +24382,19 @@
         <v>-0.8902676827503226</v>
       </c>
       <c r="AD116">
-        <v>-0.706577181812413</v>
+        <v>-1.061533701979905</v>
       </c>
       <c r="AE116">
-        <v>0.7944007497574752</v>
+        <v>0.8011877717595373</v>
       </c>
       <c r="AF116">
-        <v>-0.6860686267146576</v>
+        <v>-0.7752189153499678</v>
       </c>
       <c r="AG116">
-        <v>-0.2521206876748739</v>
+        <v>0.321890410773492</v>
       </c>
       <c r="AH116">
-        <v>-0.02346527229411917</v>
+        <v>-0.1688487708634836</v>
       </c>
       <c r="AI116">
         <v>-0.5139857686384602</v>
@@ -24517,19 +24517,19 @@
         <v>0.1349669495563162</v>
       </c>
       <c r="F117">
-        <v>-1.725542344911338</v>
+        <v>-1.927563976970878</v>
       </c>
       <c r="G117">
-        <v>1.549008941808705</v>
+        <v>1.215909479923758</v>
       </c>
       <c r="H117">
-        <v>-0.005462128393742105</v>
+        <v>-0.2252334219934503</v>
       </c>
       <c r="I117">
-        <v>1.015887490868089</v>
+        <v>0.628875219105935</v>
       </c>
       <c r="J117">
-        <v>1.415369393883473</v>
+        <v>1.626128350674778</v>
       </c>
       <c r="K117">
         <v>-1.125619081341349</v>
@@ -24589,19 +24589,19 @@
         <v>0.165760775060164</v>
       </c>
       <c r="AD117">
-        <v>-2.330926970631769</v>
+        <v>-2.954369438276726</v>
       </c>
       <c r="AE117">
-        <v>0.3575490389108458</v>
+        <v>0.5919826793644207</v>
       </c>
       <c r="AF117">
-        <v>-0.0862381113936137</v>
+        <v>-0.05076027849290055</v>
       </c>
       <c r="AG117">
-        <v>-0.6107220141402399</v>
+        <v>0.7080756263354642</v>
       </c>
       <c r="AH117">
-        <v>0.02481165898085299</v>
+        <v>-0.4464192109296695</v>
       </c>
       <c r="AI117">
         <v>-1.005991649624693</v>
@@ -24724,19 +24724,19 @@
         <v>0.1335014893141034</v>
       </c>
       <c r="F118">
-        <v>1.928086612772548</v>
+        <v>1.806298194528247</v>
       </c>
       <c r="G118">
-        <v>-0.6654110962111668</v>
+        <v>-0.1947091623426197</v>
       </c>
       <c r="H118">
-        <v>1.29996371908064</v>
+        <v>1.470085715364723</v>
       </c>
       <c r="I118">
-        <v>1.794586492752021</v>
+        <v>1.598735450414922</v>
       </c>
       <c r="J118">
-        <v>0.7970324909446884</v>
+        <v>1.068456791875845</v>
       </c>
       <c r="K118">
         <v>2.584022852013891</v>
@@ -24796,19 +24796,19 @@
         <v>0.307113264425172</v>
       </c>
       <c r="AD118">
-        <v>2.535728723532479</v>
+        <v>2.963107659313874</v>
       </c>
       <c r="AE118">
-        <v>0.8561328640013834</v>
+        <v>0.5304696967069292</v>
       </c>
       <c r="AF118">
-        <v>-0.7912678596903487</v>
+        <v>-1.032545854434041</v>
       </c>
       <c r="AG118">
-        <v>0.101229758116166</v>
+        <v>0.5917545118144041</v>
       </c>
       <c r="AH118">
-        <v>0.1613837846509327</v>
+        <v>0.2558197729915586</v>
       </c>
       <c r="AI118">
         <v>0.6031004552172237</v>
@@ -24931,19 +24931,19 @@
         <v>0.1013896355553495</v>
       </c>
       <c r="F119">
-        <v>-1.719780368534306</v>
+        <v>-1.736801641752052</v>
       </c>
       <c r="G119">
-        <v>0.5679831591777741</v>
+        <v>0.2041704143951392</v>
       </c>
       <c r="H119">
-        <v>-2.157441538232904</v>
+        <v>-2.220998032071276</v>
       </c>
       <c r="I119">
-        <v>-1.103941985905112</v>
+        <v>-0.9478367743685023</v>
       </c>
       <c r="J119">
-        <v>-0.3270627994395012</v>
+        <v>-0.6977570397378938</v>
       </c>
       <c r="K119">
         <v>-0.7588558599326671</v>
@@ -25003,19 +25003,19 @@
         <v>-0.9158359630010828</v>
       </c>
       <c r="AD119">
-        <v>-0.3795954339276689</v>
+        <v>-0.6121449645564653</v>
       </c>
       <c r="AE119">
-        <v>-0.03861113444944195</v>
+        <v>-0.04155139807497718</v>
       </c>
       <c r="AF119">
-        <v>-0.8152614104281863</v>
+        <v>-0.7903105254966969</v>
       </c>
       <c r="AG119">
-        <v>-0.3015246399042431</v>
+        <v>-0.3379368491090963</v>
       </c>
       <c r="AH119">
-        <v>-0.00355953639740095</v>
+        <v>-0.3734743300762487</v>
       </c>
       <c r="AI119">
         <v>-0.3418377118532877</v>
@@ -25138,19 +25138,19 @@
         <v>-0.1023930276848194</v>
       </c>
       <c r="F120">
-        <v>0.45674246113926</v>
+        <v>0.2915101088943</v>
       </c>
       <c r="G120">
-        <v>-0.1394254001708664</v>
+        <v>0.07277356031892938</v>
       </c>
       <c r="H120">
-        <v>0.5727958350397676</v>
+        <v>0.7265147461104533</v>
       </c>
       <c r="I120">
-        <v>1.71675330061941</v>
+        <v>2.035715155096988</v>
       </c>
       <c r="J120">
-        <v>-1.504920748429658</v>
+        <v>-1.038098086026974</v>
       </c>
       <c r="K120">
         <v>3.071406861965161</v>
@@ -25210,19 +25210,19 @@
         <v>-1.895689087842813</v>
       </c>
       <c r="AD120">
-        <v>2.649002635117879</v>
+        <v>3.483204026568258</v>
       </c>
       <c r="AE120">
-        <v>1.08834145902653</v>
+        <v>0.8353819411386422</v>
       </c>
       <c r="AF120">
-        <v>0.09441982104314617</v>
+        <v>-0.1060470143563892</v>
       </c>
       <c r="AG120">
-        <v>-0.02213229402703127</v>
+        <v>0.798171374433889</v>
       </c>
       <c r="AH120">
-        <v>0.1095495792758815</v>
+        <v>0.1655871088623988</v>
       </c>
       <c r="AI120">
         <v>-0.6747360204779949</v>
@@ -25345,19 +25345,19 @@
         <v>0.01821023129272615</v>
       </c>
       <c r="F121">
-        <v>-0.1405871102720522</v>
+        <v>-0.3447578173433867</v>
       </c>
       <c r="G121">
-        <v>0.8391525413517219</v>
+        <v>0.8388876522849597</v>
       </c>
       <c r="H121">
-        <v>-0.6517082331721459</v>
+        <v>-0.6296118968401365</v>
       </c>
       <c r="I121">
-        <v>1.51980073524537</v>
+        <v>1.65319105622267</v>
       </c>
       <c r="J121">
-        <v>-0.7041544289877024</v>
+        <v>-0.3228052083964241</v>
       </c>
       <c r="K121">
         <v>-10.38639614286582</v>
@@ -25417,19 +25417,19 @@
         <v>1.177216939962532</v>
       </c>
       <c r="AD121">
-        <v>-4.303200073939087</v>
+        <v>-5.229433177824988</v>
       </c>
       <c r="AE121">
-        <v>0.04116990319698477</v>
+        <v>0.5139023523349905</v>
       </c>
       <c r="AF121">
-        <v>1.359700196399688</v>
+        <v>1.503678014998345</v>
       </c>
       <c r="AG121">
-        <v>-0.1887825817073567</v>
+        <v>0.03564608024239556</v>
       </c>
       <c r="AH121">
-        <v>0.177803766429488</v>
+        <v>-0.2058349448053436</v>
       </c>
       <c r="AI121">
         <v>2.387891508117971</v>
@@ -25552,19 +25552,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F122">
-        <v>-1.214672089520727</v>
+        <v>-1.40080284464883</v>
       </c>
       <c r="G122">
-        <v>0.4045411371041382</v>
+        <v>0.3267171211422746</v>
       </c>
       <c r="H122">
-        <v>2.110688029323779</v>
+        <v>2.050643670256195</v>
       </c>
       <c r="I122">
-        <v>-0.1638628488506555</v>
+        <v>-0.03321691811000078</v>
       </c>
       <c r="J122">
-        <v>-0.9545968697300451</v>
+        <v>-0.6791210167323337</v>
       </c>
       <c r="K122">
         <v>0.7238371516204137</v>
@@ -25624,19 +25624,19 @@
         <v>-0.6420404287530234</v>
       </c>
       <c r="AD122">
-        <v>-0.941428016342206</v>
+        <v>-0.764003908331258</v>
       </c>
       <c r="AE122">
-        <v>0.5526379906451673</v>
+        <v>0.7528356577560068</v>
       </c>
       <c r="AF122">
-        <v>1.083305507621273</v>
+        <v>1.13005100540495</v>
       </c>
       <c r="AG122">
-        <v>-0.1248283962460986</v>
+        <v>0.2573954703418805</v>
       </c>
       <c r="AH122">
-        <v>-0.133784575704458</v>
+        <v>-0.06998695218385811</v>
       </c>
       <c r="AI122">
         <v>-0.6809671420522195</v>
@@ -25759,19 +25759,19 @@
         <v>-0.03025797074556105</v>
       </c>
       <c r="F123">
-        <v>0.9631855471952256</v>
+        <v>0.8290174279165382</v>
       </c>
       <c r="G123">
-        <v>0.7735006734832731</v>
+        <v>0.8911349570192637</v>
       </c>
       <c r="H123">
-        <v>-1.377209995357213</v>
+        <v>-1.33891035639256</v>
       </c>
       <c r="I123">
-        <v>0.619159790167094</v>
+        <v>0.6048282966415768</v>
       </c>
       <c r="J123">
-        <v>0.3270015219536707</v>
+        <v>0.2405458353282231</v>
       </c>
       <c r="K123">
         <v>0.3191702434349739</v>
@@ -25831,19 +25831,19 @@
         <v>0.198668049507886</v>
       </c>
       <c r="AD123">
-        <v>-0.4910190445850966</v>
+        <v>-1.143335527897648</v>
       </c>
       <c r="AE123">
-        <v>-0.495262012792087</v>
+        <v>-0.5212964708172999</v>
       </c>
       <c r="AF123">
-        <v>-0.411398458127453</v>
+        <v>-0.4994044384099701</v>
       </c>
       <c r="AG123">
-        <v>-0.3904868742829362</v>
+        <v>0.4604526172224903</v>
       </c>
       <c r="AH123">
-        <v>0.01386892132536104</v>
+        <v>-0.2807902210214892</v>
       </c>
       <c r="AI123">
         <v>0.4159380854797215</v>
@@ -25966,19 +25966,19 @@
         <v>0.1298378387085714</v>
       </c>
       <c r="F124">
-        <v>-1.367333706667223</v>
+        <v>-1.510620393342876</v>
       </c>
       <c r="G124">
-        <v>0.6062073676045455</v>
+        <v>0.4195362476243811</v>
       </c>
       <c r="H124">
-        <v>0.19442131135778</v>
+        <v>0.1434174619656537</v>
       </c>
       <c r="I124">
-        <v>-0.07313116850185172</v>
+        <v>0.1126007671844668</v>
       </c>
       <c r="J124">
-        <v>-0.9428882420218879</v>
+        <v>-0.8032828341786751</v>
       </c>
       <c r="K124">
         <v>-0.4742514665773516</v>
@@ -26038,19 +26038,19 @@
         <v>-0.574441062070133</v>
       </c>
       <c r="AD124">
-        <v>0.5864444800012237</v>
+        <v>1.038333745631256</v>
       </c>
       <c r="AE124">
-        <v>-0.1399607547196105</v>
+        <v>-0.1103708348718692</v>
       </c>
       <c r="AF124">
-        <v>0.6819033288196421</v>
+        <v>0.7248645991442926</v>
       </c>
       <c r="AG124">
-        <v>-0.8861799591207351</v>
+        <v>0.3870931194971197</v>
       </c>
       <c r="AH124">
-        <v>-0.09853606370684297</v>
+        <v>-0.8226062516766237</v>
       </c>
       <c r="AI124">
         <v>-1.834032991076335</v>
@@ -26173,19 +26173,19 @@
         <v>0.7472090969108418</v>
       </c>
       <c r="F125">
-        <v>-0.8546209191122812</v>
+        <v>-0.8459622557472115</v>
       </c>
       <c r="G125">
-        <v>-0.3919732948977389</v>
+        <v>-0.4853713209410399</v>
       </c>
       <c r="H125">
-        <v>0.5057713420837492</v>
+        <v>0.4801368091418463</v>
       </c>
       <c r="I125">
-        <v>0.9455774211955992</v>
+        <v>0.7377322943692965</v>
       </c>
       <c r="J125">
-        <v>0.5940639704629456</v>
+        <v>0.9048054566903607</v>
       </c>
       <c r="K125">
         <v>-4.830642999749935</v>
@@ -26245,19 +26245,19 @@
         <v>-0.3601713592445956</v>
       </c>
       <c r="AD125">
-        <v>-2.268921947371267</v>
+        <v>-2.81151165484927</v>
       </c>
       <c r="AE125">
-        <v>-0.3163671156993469</v>
+        <v>-0.1201088212769386</v>
       </c>
       <c r="AF125">
-        <v>-0.5396935904020463</v>
+        <v>-0.3410612914180324</v>
       </c>
       <c r="AG125">
-        <v>0.114074878588167</v>
+        <v>-1.309368432541559</v>
       </c>
       <c r="AH125">
-        <v>-0.41893776871865</v>
+        <v>-0.1972014579789563</v>
       </c>
       <c r="AI125">
         <v>3.904884523928104</v>
@@ -26380,19 +26380,19 @@
         <v>0.7907604079465506</v>
       </c>
       <c r="F126">
-        <v>-2.656786934020019</v>
+        <v>-2.337586350202472</v>
       </c>
       <c r="G126">
-        <v>-1.519811175834576</v>
+        <v>-2.001434391262966</v>
       </c>
       <c r="H126">
-        <v>-2.153479509300798</v>
+        <v>-2.141749544741044</v>
       </c>
       <c r="I126">
-        <v>0.5110718999120015</v>
+        <v>0.3964582242063094</v>
       </c>
       <c r="J126">
-        <v>0.8605014104949255</v>
+        <v>0.6548472279946823</v>
       </c>
       <c r="K126">
         <v>-5.100130427556864</v>
@@ -26452,19 +26452,19 @@
         <v>0.9821172394484989</v>
       </c>
       <c r="AD126">
-        <v>-3.154676979078838</v>
+        <v>-4.338295233778021</v>
       </c>
       <c r="AE126">
-        <v>0.3424759759414758</v>
+        <v>0.545600961314387</v>
       </c>
       <c r="AF126">
-        <v>-1.11971483509866</v>
+        <v>-1.091672766034065</v>
       </c>
       <c r="AG126">
-        <v>-0.1722604718368709</v>
+        <v>-0.135698952755243</v>
       </c>
       <c r="AH126">
-        <v>0.03131350033066337</v>
+        <v>-0.1907596443844014</v>
       </c>
       <c r="AI126">
         <v>0.2808500888756244</v>
